--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="389">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -829,6 +829,9 @@
     <t>['28', '32', '38', '82']</t>
   </si>
   <si>
+    <t>['15', '22', '49', '72', '80']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1539,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP287"/>
+  <dimension ref="A1:BP288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2001,7 +2004,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2413,7 +2416,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -3031,7 +3034,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -3237,7 +3240,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3443,7 +3446,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3649,7 +3652,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4139,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ13">
         <v>1.08</v>
@@ -4679,7 +4682,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5091,7 +5094,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5297,7 +5300,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -5996,7 +5999,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ22">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6121,7 +6124,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6533,7 +6536,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6739,7 +6742,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7563,7 +7566,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -9005,7 +9008,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9211,7 +9214,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9623,7 +9626,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10035,7 +10038,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10319,7 +10322,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ43">
         <v>0.91</v>
@@ -10447,7 +10450,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10528,7 +10531,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ44">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR44">
         <v>1.2</v>
@@ -10653,7 +10656,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -11271,7 +11274,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11683,7 +11686,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11889,7 +11892,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -14567,7 +14570,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14645,7 +14648,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ64">
         <v>0.92</v>
@@ -14979,7 +14982,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15266,7 +15269,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ67">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR67">
         <v>1.34</v>
@@ -15597,7 +15600,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15803,7 +15806,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16009,7 +16012,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16215,7 +16218,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16627,7 +16630,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16833,7 +16836,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17039,7 +17042,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17451,7 +17454,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17738,7 +17741,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ79">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -18481,7 +18484,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -18971,7 +18974,7 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ85">
         <v>0.91</v>
@@ -19717,7 +19720,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -20129,7 +20132,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20335,7 +20338,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20541,7 +20544,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -20953,7 +20956,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21159,7 +21162,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -21777,7 +21780,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q99">
         <v>4.5</v>
@@ -21983,7 +21986,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22061,7 +22064,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ100">
         <v>1.1</v>
@@ -22395,7 +22398,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22601,7 +22604,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22807,7 +22810,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23219,7 +23222,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -24124,7 +24127,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ110">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR110">
         <v>1.38</v>
@@ -24661,7 +24664,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24867,7 +24870,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25485,7 +25488,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q117">
         <v>2.05</v>
@@ -25691,7 +25694,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25897,7 +25900,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26103,7 +26106,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26721,7 +26724,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -27133,7 +27136,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27545,7 +27548,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27751,7 +27754,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -28369,7 +28372,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28575,7 +28578,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28781,7 +28784,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28987,7 +28990,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29193,7 +29196,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29399,7 +29402,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29605,7 +29608,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -29686,7 +29689,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ137">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR137">
         <v>1.32</v>
@@ -29811,7 +29814,7 @@
         <v>185</v>
       </c>
       <c r="P138" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q138">
         <v>2.5</v>
@@ -30223,7 +30226,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -30301,7 +30304,7 @@
         <v>0.67</v>
       </c>
       <c r="AP140">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ140">
         <v>0.75</v>
@@ -30429,7 +30432,7 @@
         <v>101</v>
       </c>
       <c r="P141" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q141">
         <v>3</v>
@@ -31253,7 +31256,7 @@
         <v>101</v>
       </c>
       <c r="P145" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31871,7 +31874,7 @@
         <v>192</v>
       </c>
       <c r="P148" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -32695,7 +32698,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32901,7 +32904,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33313,7 +33316,7 @@
         <v>196</v>
       </c>
       <c r="P155" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33725,7 +33728,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -34012,7 +34015,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ158">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR158">
         <v>1.15</v>
@@ -34549,7 +34552,7 @@
         <v>202</v>
       </c>
       <c r="P161" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q161">
         <v>3.2</v>
@@ -35167,7 +35170,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35373,7 +35376,7 @@
         <v>101</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q165">
         <v>2.63</v>
@@ -35579,7 +35582,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35785,7 +35788,7 @@
         <v>205</v>
       </c>
       <c r="P167" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -35863,7 +35866,7 @@
         <v>1.67</v>
       </c>
       <c r="AP167">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ167">
         <v>1.42</v>
@@ -36197,7 +36200,7 @@
         <v>207</v>
       </c>
       <c r="P169" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q169">
         <v>2.5</v>
@@ -37021,7 +37024,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37227,7 +37230,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -38257,7 +38260,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -39081,7 +39084,7 @@
         <v>214</v>
       </c>
       <c r="P183" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q183">
         <v>3.2</v>
@@ -39493,7 +39496,7 @@
         <v>185</v>
       </c>
       <c r="P185" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q185">
         <v>3.4</v>
@@ -39905,7 +39908,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40192,7 +40195,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ188">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR188">
         <v>1.31</v>
@@ -40523,7 +40526,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40729,7 +40732,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40935,7 +40938,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41965,7 +41968,7 @@
         <v>221</v>
       </c>
       <c r="P197" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42043,7 +42046,7 @@
         <v>1.29</v>
       </c>
       <c r="AP197">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ197">
         <v>1.58</v>
@@ -42171,7 +42174,7 @@
         <v>101</v>
       </c>
       <c r="P198" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q198">
         <v>3.75</v>
@@ -42377,7 +42380,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42995,7 +42998,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43201,7 +43204,7 @@
         <v>208</v>
       </c>
       <c r="P203" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43407,7 +43410,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -43819,7 +43822,7 @@
         <v>226</v>
       </c>
       <c r="P206" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q206">
         <v>2.85</v>
@@ -44231,7 +44234,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44437,7 +44440,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44515,7 +44518,7 @@
         <v>1.56</v>
       </c>
       <c r="AP209">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ209">
         <v>1.54</v>
@@ -44849,7 +44852,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -45673,7 +45676,7 @@
         <v>234</v>
       </c>
       <c r="P215" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -45960,7 +45963,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ216">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR216">
         <v>1.49</v>
@@ -46085,7 +46088,7 @@
         <v>236</v>
       </c>
       <c r="P217" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46291,7 +46294,7 @@
         <v>101</v>
       </c>
       <c r="P218" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46703,7 +46706,7 @@
         <v>101</v>
       </c>
       <c r="P220" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47115,7 +47118,7 @@
         <v>239</v>
       </c>
       <c r="P222" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q222">
         <v>2.38</v>
@@ -47399,7 +47402,7 @@
         <v>0.89</v>
       </c>
       <c r="AP223">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ223">
         <v>0.75</v>
@@ -48145,7 +48148,7 @@
         <v>101</v>
       </c>
       <c r="P227" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48763,7 +48766,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48969,7 +48972,7 @@
         <v>101</v>
       </c>
       <c r="P231" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q231">
         <v>3.4</v>
@@ -49175,7 +49178,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49381,7 +49384,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -50080,7 +50083,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ236">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR236">
         <v>1.36</v>
@@ -50205,7 +50208,7 @@
         <v>244</v>
       </c>
       <c r="P237" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q237">
         <v>4.5</v>
@@ -50411,7 +50414,7 @@
         <v>101</v>
       </c>
       <c r="P238" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q238">
         <v>5.5</v>
@@ -50823,7 +50826,7 @@
         <v>246</v>
       </c>
       <c r="P240" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q240">
         <v>2.88</v>
@@ -51235,7 +51238,7 @@
         <v>101</v>
       </c>
       <c r="P242" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q242">
         <v>3.75</v>
@@ -51441,7 +51444,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -51931,7 +51934,7 @@
         <v>1.7</v>
       </c>
       <c r="AP245">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ245">
         <v>1.5</v>
@@ -52265,7 +52268,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -52471,7 +52474,7 @@
         <v>249</v>
       </c>
       <c r="P248" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q248">
         <v>2.38</v>
@@ -53089,7 +53092,7 @@
         <v>101</v>
       </c>
       <c r="P251" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q251">
         <v>2.5</v>
@@ -53707,7 +53710,7 @@
         <v>254</v>
       </c>
       <c r="P254" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q254">
         <v>2.25</v>
@@ -53913,7 +53916,7 @@
         <v>255</v>
       </c>
       <c r="P255" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q255">
         <v>2.1</v>
@@ -54119,7 +54122,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -54609,7 +54612,7 @@
         <v>0.75</v>
       </c>
       <c r="AP258">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ258">
         <v>0.6899999999999999</v>
@@ -55355,7 +55358,7 @@
         <v>259</v>
       </c>
       <c r="P262" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q262">
         <v>3.6</v>
@@ -56591,7 +56594,7 @@
         <v>101</v>
       </c>
       <c r="P268" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -56797,7 +56800,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q269">
         <v>2.4</v>
@@ -57003,7 +57006,7 @@
         <v>184</v>
       </c>
       <c r="P270" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q270">
         <v>3.25</v>
@@ -57290,7 +57293,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ271">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR271">
         <v>1.29</v>
@@ -57415,7 +57418,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57621,7 +57624,7 @@
         <v>264</v>
       </c>
       <c r="P273" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q273">
         <v>2.75</v>
@@ -58033,7 +58036,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q275">
         <v>2.88</v>
@@ -58239,7 +58242,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q276">
         <v>3.1</v>
@@ -58445,7 +58448,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q277">
         <v>3.4</v>
@@ -58651,7 +58654,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -58857,7 +58860,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -60093,7 +60096,7 @@
         <v>101</v>
       </c>
       <c r="P285" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60299,7 +60302,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q286">
         <v>2.6</v>
@@ -60505,7 +60508,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -60662,6 +60665,212 @@
       </c>
       <c r="BP287">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="288" spans="1:68">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>7476854</v>
+      </c>
+      <c r="C288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288" s="2">
+        <v>45668.39583333334</v>
+      </c>
+      <c r="F288">
+        <v>26</v>
+      </c>
+      <c r="G288" t="s">
+        <v>81</v>
+      </c>
+      <c r="H288" t="s">
+        <v>80</v>
+      </c>
+      <c r="I288">
+        <v>2</v>
+      </c>
+      <c r="J288">
+        <v>1</v>
+      </c>
+      <c r="K288">
+        <v>3</v>
+      </c>
+      <c r="L288">
+        <v>5</v>
+      </c>
+      <c r="M288">
+        <v>1</v>
+      </c>
+      <c r="N288">
+        <v>6</v>
+      </c>
+      <c r="O288" t="s">
+        <v>271</v>
+      </c>
+      <c r="P288" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q288">
+        <v>2.1</v>
+      </c>
+      <c r="R288">
+        <v>2.25</v>
+      </c>
+      <c r="S288">
+        <v>6</v>
+      </c>
+      <c r="T288">
+        <v>1.4</v>
+      </c>
+      <c r="U288">
+        <v>2.75</v>
+      </c>
+      <c r="V288">
+        <v>2.75</v>
+      </c>
+      <c r="W288">
+        <v>1.4</v>
+      </c>
+      <c r="X288">
+        <v>8</v>
+      </c>
+      <c r="Y288">
+        <v>1.08</v>
+      </c>
+      <c r="Z288">
+        <v>1.6</v>
+      </c>
+      <c r="AA288">
+        <v>4</v>
+      </c>
+      <c r="AB288">
+        <v>5</v>
+      </c>
+      <c r="AC288">
+        <v>1.05</v>
+      </c>
+      <c r="AD288">
+        <v>9.5</v>
+      </c>
+      <c r="AE288">
+        <v>1.3</v>
+      </c>
+      <c r="AF288">
+        <v>3.45</v>
+      </c>
+      <c r="AG288">
+        <v>1.85</v>
+      </c>
+      <c r="AH288">
+        <v>1.83</v>
+      </c>
+      <c r="AI288">
+        <v>1.91</v>
+      </c>
+      <c r="AJ288">
+        <v>1.8</v>
+      </c>
+      <c r="AK288">
+        <v>1.13</v>
+      </c>
+      <c r="AL288">
+        <v>1.2</v>
+      </c>
+      <c r="AM288">
+        <v>2.35</v>
+      </c>
+      <c r="AN288">
+        <v>2.42</v>
+      </c>
+      <c r="AO288">
+        <v>0.73</v>
+      </c>
+      <c r="AP288">
+        <v>2.46</v>
+      </c>
+      <c r="AQ288">
+        <v>0.67</v>
+      </c>
+      <c r="AR288">
+        <v>1.53</v>
+      </c>
+      <c r="AS288">
+        <v>1.23</v>
+      </c>
+      <c r="AT288">
+        <v>2.76</v>
+      </c>
+      <c r="AU288">
+        <v>10</v>
+      </c>
+      <c r="AV288">
+        <v>2</v>
+      </c>
+      <c r="AW288">
+        <v>9</v>
+      </c>
+      <c r="AX288">
+        <v>9</v>
+      </c>
+      <c r="AY288">
+        <v>21</v>
+      </c>
+      <c r="AZ288">
+        <v>14</v>
+      </c>
+      <c r="BA288">
+        <v>3</v>
+      </c>
+      <c r="BB288">
+        <v>2</v>
+      </c>
+      <c r="BC288">
+        <v>5</v>
+      </c>
+      <c r="BD288">
+        <v>1.49</v>
+      </c>
+      <c r="BE288">
+        <v>6.75</v>
+      </c>
+      <c r="BF288">
+        <v>2.9</v>
+      </c>
+      <c r="BG288">
+        <v>1.3</v>
+      </c>
+      <c r="BH288">
+        <v>3.15</v>
+      </c>
+      <c r="BI288">
+        <v>1.5</v>
+      </c>
+      <c r="BJ288">
+        <v>2.33</v>
+      </c>
+      <c r="BK288">
+        <v>1.82</v>
+      </c>
+      <c r="BL288">
+        <v>1.86</v>
+      </c>
+      <c r="BM288">
+        <v>2.3</v>
+      </c>
+      <c r="BN288">
+        <v>1.54</v>
+      </c>
+      <c r="BO288">
+        <v>2.9</v>
+      </c>
+      <c r="BP288">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="389">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1542,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP288"/>
+  <dimension ref="A1:BP289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2291,7 +2291,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ4">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23">
         <v>2.09</v>
@@ -9704,7 +9704,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ40">
         <v>1.54</v>
@@ -10737,7 +10737,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ45">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR45">
         <v>1.02</v>
@@ -14236,7 +14236,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ62">
         <v>0.6899999999999999</v>
@@ -15475,7 +15475,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ68">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR68">
         <v>1.88</v>
@@ -16708,7 +16708,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ74">
         <v>0.75</v>
@@ -19801,7 +19801,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ89">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR89">
         <v>0.82</v>
@@ -23712,7 +23712,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -27011,7 +27011,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ124">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR124">
         <v>1.08</v>
@@ -28656,7 +28656,7 @@
         <v>1.4</v>
       </c>
       <c r="AP132">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ132">
         <v>1.5</v>
@@ -31543,7 +31543,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ146">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR146">
         <v>1.61</v>
@@ -33600,7 +33600,7 @@
         <v>1.17</v>
       </c>
       <c r="AP156">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -35869,7 +35869,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ167">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR167">
         <v>1.52</v>
@@ -41016,7 +41016,7 @@
         <v>0.88</v>
       </c>
       <c r="AP192">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ192">
         <v>1.08</v>
@@ -41843,7 +41843,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ196">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR196">
         <v>1.37</v>
@@ -42461,7 +42461,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ199">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR199">
         <v>1.51</v>
@@ -46578,7 +46578,7 @@
         <v>1.57</v>
       </c>
       <c r="AP219">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ219">
         <v>1.1</v>
@@ -49053,7 +49053,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ231">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR231">
         <v>1.28</v>
@@ -50904,7 +50904,7 @@
         <v>1.9</v>
       </c>
       <c r="AP240">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ240">
         <v>1.46</v>
@@ -52967,7 +52967,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ250">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR250">
         <v>1.29</v>
@@ -55851,7 +55851,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ264">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR264">
         <v>1.35</v>
@@ -57496,7 +57496,7 @@
         <v>1</v>
       </c>
       <c r="AP272">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ272">
         <v>0.91</v>
@@ -60870,6 +60870,212 @@
         <v>2.9</v>
       </c>
       <c r="BP288">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7476853</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45668.5</v>
+      </c>
+      <c r="F289">
+        <v>26</v>
+      </c>
+      <c r="G289" t="s">
+        <v>91</v>
+      </c>
+      <c r="H289" t="s">
+        <v>86</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>0</v>
+      </c>
+      <c r="L289">
+        <v>0</v>
+      </c>
+      <c r="M289">
+        <v>0</v>
+      </c>
+      <c r="N289">
+        <v>0</v>
+      </c>
+      <c r="O289" t="s">
+        <v>101</v>
+      </c>
+      <c r="P289" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q289">
+        <v>3.4</v>
+      </c>
+      <c r="R289">
+        <v>2.1</v>
+      </c>
+      <c r="S289">
+        <v>3.25</v>
+      </c>
+      <c r="T289">
+        <v>1.44</v>
+      </c>
+      <c r="U289">
+        <v>2.63</v>
+      </c>
+      <c r="V289">
+        <v>3.25</v>
+      </c>
+      <c r="W289">
+        <v>1.33</v>
+      </c>
+      <c r="X289">
+        <v>9</v>
+      </c>
+      <c r="Y289">
+        <v>1.07</v>
+      </c>
+      <c r="Z289">
+        <v>2.7</v>
+      </c>
+      <c r="AA289">
+        <v>3.3</v>
+      </c>
+      <c r="AB289">
+        <v>2.5</v>
+      </c>
+      <c r="AC289">
+        <v>1.06</v>
+      </c>
+      <c r="AD289">
+        <v>8.5</v>
+      </c>
+      <c r="AE289">
+        <v>1.33</v>
+      </c>
+      <c r="AF289">
+        <v>3.2</v>
+      </c>
+      <c r="AG289">
+        <v>2.05</v>
+      </c>
+      <c r="AH289">
+        <v>1.75</v>
+      </c>
+      <c r="AI289">
+        <v>1.8</v>
+      </c>
+      <c r="AJ289">
+        <v>1.91</v>
+      </c>
+      <c r="AK289">
+        <v>1.5</v>
+      </c>
+      <c r="AL289">
+        <v>1.28</v>
+      </c>
+      <c r="AM289">
+        <v>1.42</v>
+      </c>
+      <c r="AN289">
+        <v>1.27</v>
+      </c>
+      <c r="AO289">
+        <v>1.42</v>
+      </c>
+      <c r="AP289">
+        <v>1.25</v>
+      </c>
+      <c r="AQ289">
+        <v>1.38</v>
+      </c>
+      <c r="AR289">
+        <v>1.31</v>
+      </c>
+      <c r="AS289">
+        <v>1.15</v>
+      </c>
+      <c r="AT289">
+        <v>2.46</v>
+      </c>
+      <c r="AU289">
+        <v>3</v>
+      </c>
+      <c r="AV289">
+        <v>2</v>
+      </c>
+      <c r="AW289">
+        <v>16</v>
+      </c>
+      <c r="AX289">
+        <v>6</v>
+      </c>
+      <c r="AY289">
+        <v>23</v>
+      </c>
+      <c r="AZ289">
+        <v>10</v>
+      </c>
+      <c r="BA289">
+        <v>11</v>
+      </c>
+      <c r="BB289">
+        <v>6</v>
+      </c>
+      <c r="BC289">
+        <v>17</v>
+      </c>
+      <c r="BD289">
+        <v>2.08</v>
+      </c>
+      <c r="BE289">
+        <v>6.4</v>
+      </c>
+      <c r="BF289">
+        <v>1.91</v>
+      </c>
+      <c r="BG289">
+        <v>1.29</v>
+      </c>
+      <c r="BH289">
+        <v>3.2</v>
+      </c>
+      <c r="BI289">
+        <v>1.49</v>
+      </c>
+      <c r="BJ289">
+        <v>2.4</v>
+      </c>
+      <c r="BK289">
+        <v>1.81</v>
+      </c>
+      <c r="BL289">
+        <v>1.88</v>
+      </c>
+      <c r="BM289">
+        <v>2.28</v>
+      </c>
+      <c r="BN289">
+        <v>1.55</v>
+      </c>
+      <c r="BO289">
+        <v>2.9</v>
+      </c>
+      <c r="BP289">
         <v>1.34</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
@@ -60807,22 +60807,22 @@
         <v>2.76</v>
       </c>
       <c r="AU288">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV288">
         <v>2</v>
       </c>
       <c r="AW288">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX288">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AY288">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ288">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA288">
         <v>3</v>
@@ -61013,22 +61013,22 @@
         <v>2.46</v>
       </c>
       <c r="AU289">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV289">
         <v>2</v>
       </c>
       <c r="AW289">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AX289">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY289">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ289">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA289">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="400">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -832,6 +832,21 @@
     <t>['15', '22', '49', '72', '80']</t>
   </si>
   <si>
+    <t>['34', '56']</t>
+  </si>
+  <si>
+    <t>['29', '62', '77']</t>
+  </si>
+  <si>
+    <t>['32', '46', '66', '81']</t>
+  </si>
+  <si>
+    <t>['8', '87']</t>
+  </si>
+  <si>
+    <t>['48', '81']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1181,6 +1196,24 @@
   </si>
   <si>
     <t>['18', '59']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['12', '33']</t>
+  </si>
+  <si>
+    <t>['4']</t>
+  </si>
+  <si>
+    <t>['2', '11']</t>
+  </si>
+  <si>
+    <t>['14', '85']</t>
+  </si>
+  <si>
+    <t>['16', '27', '63']</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP289"/>
+  <dimension ref="A1:BP301"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2004,7 +2037,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2082,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ3">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2291,7 +2324,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ4">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2416,7 +2449,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -2497,7 +2530,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ5">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3034,7 +3067,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -3112,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ8">
         <v>0.75</v>
@@ -3240,7 +3273,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3318,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ9">
         <v>1.58</v>
@@ -3446,7 +3479,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3527,7 +3560,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ10">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3652,7 +3685,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3730,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ11">
         <v>1.71</v>
@@ -3939,7 +3972,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ12">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4142,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13">
         <v>1.08</v>
@@ -4348,10 +4381,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ14">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4554,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ15">
         <v>1.45</v>
@@ -4682,7 +4715,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4760,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4969,7 +5002,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5094,7 +5127,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5175,7 +5208,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ18">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5300,7 +5333,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -5378,10 +5411,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ19">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5584,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5793,7 +5826,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5996,10 +6029,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6124,7 +6157,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6202,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23">
         <v>2.09</v>
@@ -6536,7 +6569,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6617,7 +6650,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ25">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6742,7 +6775,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7566,7 +7599,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -9008,7 +9041,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9214,7 +9247,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9292,10 +9325,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -9498,10 +9531,10 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR39">
         <v>1.62</v>
@@ -9626,7 +9659,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9704,10 +9737,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ40">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -9910,10 +9943,10 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ41">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR41">
         <v>1.1</v>
@@ -10038,7 +10071,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10116,10 +10149,10 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR42">
         <v>1.15</v>
@@ -10322,10 +10355,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ43">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR43">
         <v>0.97</v>
@@ -10450,7 +10483,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10528,10 +10561,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ44">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR44">
         <v>1.2</v>
@@ -10656,7 +10689,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10734,10 +10767,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ45">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR45">
         <v>1.02</v>
@@ -10940,10 +10973,10 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ46">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR46">
         <v>2.58</v>
@@ -11146,10 +11179,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ47">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR47">
         <v>1.5</v>
@@ -11274,7 +11307,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11352,10 +11385,10 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ48">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR48">
         <v>1.43</v>
@@ -11558,10 +11591,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ49">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR49">
         <v>1.1</v>
@@ -11686,7 +11719,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11892,7 +11925,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -13824,10 +13857,10 @@
         <v>1.5</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ60">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -14030,10 +14063,10 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ61">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR61">
         <v>1.47</v>
@@ -14236,10 +14269,10 @@
         <v>1.5</v>
       </c>
       <c r="AP62">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ62">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR62">
         <v>1.82</v>
@@ -14442,10 +14475,10 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ63">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR63">
         <v>1.34</v>
@@ -14570,7 +14603,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -14648,10 +14681,10 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ64">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14854,10 +14887,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR65">
         <v>1.4</v>
@@ -14982,7 +15015,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15060,10 +15093,10 @@
         <v>0.5</v>
       </c>
       <c r="AP66">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ66">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR66">
         <v>1.41</v>
@@ -15266,10 +15299,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ67">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR67">
         <v>1.34</v>
@@ -15472,10 +15505,10 @@
         <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ68">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR68">
         <v>1.88</v>
@@ -15600,7 +15633,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15678,10 +15711,10 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ69">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR69">
         <v>1.03</v>
@@ -15806,7 +15839,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -15884,10 +15917,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ70">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR70">
         <v>1.23</v>
@@ -16012,7 +16045,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16090,10 +16123,10 @@
         <v>0.5</v>
       </c>
       <c r="AP71">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ71">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -16218,7 +16251,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16296,7 +16329,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ72">
         <v>1.71</v>
@@ -16505,7 +16538,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ73">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR73">
         <v>1.28</v>
@@ -16630,7 +16663,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16708,7 +16741,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ74">
         <v>0.75</v>
@@ -16836,7 +16869,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -16914,7 +16947,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ75">
         <v>2.09</v>
@@ -17042,7 +17075,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17326,7 +17359,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ77">
         <v>1.58</v>
@@ -17454,7 +17487,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17535,7 +17568,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR78">
         <v>1.48</v>
@@ -17741,7 +17774,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ79">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -18153,7 +18186,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ81">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR81">
         <v>1.2</v>
@@ -18484,7 +18517,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -18974,10 +19007,10 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ85">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR85">
         <v>1.6</v>
@@ -19180,10 +19213,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ86">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR86">
         <v>1.1</v>
@@ -19386,10 +19419,10 @@
         <v>2.33</v>
       </c>
       <c r="AP87">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ87">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19592,7 +19625,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ88">
         <v>0.71</v>
@@ -19720,7 +19753,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -19801,7 +19834,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ89">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR89">
         <v>0.82</v>
@@ -20004,10 +20037,10 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ90">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR90">
         <v>1.27</v>
@@ -20132,7 +20165,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20213,7 +20246,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ91">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20338,7 +20371,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20419,7 +20452,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ92">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR92">
         <v>1.26</v>
@@ -20544,7 +20577,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -20622,7 +20655,7 @@
         <v>0</v>
       </c>
       <c r="AP93">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ93">
         <v>1.46</v>
@@ -20828,10 +20861,10 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ94">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR94">
         <v>1.4</v>
@@ -20956,7 +20989,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21034,10 +21067,10 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ95">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -21162,7 +21195,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -21240,10 +21273,10 @@
         <v>0.25</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ96">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR96">
         <v>1.14</v>
@@ -21780,7 +21813,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q99">
         <v>4.5</v>
@@ -21858,10 +21891,10 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ99">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR99">
         <v>1.37</v>
@@ -21986,7 +22019,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22064,10 +22097,10 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ100">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR100">
         <v>1.61</v>
@@ -22270,7 +22303,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ101">
         <v>1.46</v>
@@ -22398,7 +22431,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22604,7 +22637,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22682,10 +22715,10 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ103">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR103">
         <v>1.32</v>
@@ -22810,7 +22843,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22888,10 +22921,10 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR104">
         <v>1.27</v>
@@ -23097,7 +23130,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ105">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR105">
         <v>1</v>
@@ -23222,7 +23255,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -23300,10 +23333,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ106">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23712,7 +23745,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -24127,7 +24160,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ110">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR110">
         <v>1.38</v>
@@ -24536,7 +24569,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ112">
         <v>1.45</v>
@@ -24664,7 +24697,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24870,7 +24903,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -24951,7 +24984,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ114">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR114">
         <v>1.49</v>
@@ -25154,7 +25187,7 @@
         <v>0.25</v>
       </c>
       <c r="AP115">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ115">
         <v>1.08</v>
@@ -25488,7 +25521,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q117">
         <v>2.05</v>
@@ -25569,7 +25602,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ117">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR117">
         <v>1.54</v>
@@ -25694,7 +25727,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25775,7 +25808,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ118">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25900,7 +25933,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -25981,7 +26014,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ119">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR119">
         <v>1.15</v>
@@ -26106,7 +26139,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26184,7 +26217,7 @@
         <v>1.2</v>
       </c>
       <c r="AP120">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ120">
         <v>1.46</v>
@@ -26596,10 +26629,10 @@
         <v>0.6</v>
       </c>
       <c r="AP122">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ122">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR122">
         <v>1.16</v>
@@ -26724,7 +26757,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -26802,7 +26835,7 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ123">
         <v>0.92</v>
@@ -27011,7 +27044,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ124">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR124">
         <v>1.08</v>
@@ -27136,7 +27169,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27420,7 +27453,7 @@
         <v>0.8</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ126">
         <v>0.75</v>
@@ -27548,7 +27581,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27754,7 +27787,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -27835,7 +27868,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ128">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR128">
         <v>1.07</v>
@@ -28038,10 +28071,10 @@
         <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ129">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR129">
         <v>1.45</v>
@@ -28372,7 +28405,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28450,10 +28483,10 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ131">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR131">
         <v>1.51</v>
@@ -28578,7 +28611,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28656,10 +28689,10 @@
         <v>1.4</v>
       </c>
       <c r="AP132">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ132">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR132">
         <v>1.44</v>
@@ -28784,7 +28817,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28990,7 +29023,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29068,10 +29101,10 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ134">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR134">
         <v>1.35</v>
@@ -29196,7 +29229,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29277,7 +29310,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ135">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR135">
         <v>1.78</v>
@@ -29402,7 +29435,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29480,7 +29513,7 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ136">
         <v>2.09</v>
@@ -29608,7 +29641,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -29686,10 +29719,10 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ137">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR137">
         <v>1.32</v>
@@ -29814,7 +29847,7 @@
         <v>185</v>
       </c>
       <c r="P138" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q138">
         <v>2.5</v>
@@ -29892,7 +29925,7 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -30226,7 +30259,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -30304,7 +30337,7 @@
         <v>0.67</v>
       </c>
       <c r="AP140">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ140">
         <v>0.75</v>
@@ -30432,7 +30465,7 @@
         <v>101</v>
       </c>
       <c r="P141" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q141">
         <v>3</v>
@@ -30716,7 +30749,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ142">
         <v>0.71</v>
@@ -31128,7 +31161,7 @@
         <v>2.17</v>
       </c>
       <c r="AP144">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ144">
         <v>1.71</v>
@@ -31256,7 +31289,7 @@
         <v>101</v>
       </c>
       <c r="P145" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31334,10 +31367,10 @@
         <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ145">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR145">
         <v>1.19</v>
@@ -31543,7 +31576,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ146">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR146">
         <v>1.61</v>
@@ -31874,7 +31907,7 @@
         <v>192</v>
       </c>
       <c r="P148" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31955,7 +31988,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ148">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR148">
         <v>1.31</v>
@@ -32161,7 +32194,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ149">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR149">
         <v>1.26</v>
@@ -32367,7 +32400,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ150">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR150">
         <v>1.45</v>
@@ -32570,7 +32603,7 @@
         <v>0.67</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ151">
         <v>1.08</v>
@@ -32698,7 +32731,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32776,10 +32809,10 @@
         <v>1.67</v>
       </c>
       <c r="AP152">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ152">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR152">
         <v>1.38</v>
@@ -32904,7 +32937,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33191,7 +33224,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ154">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR154">
         <v>1.14</v>
@@ -33316,7 +33349,7 @@
         <v>196</v>
       </c>
       <c r="P155" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33394,7 +33427,7 @@
         <v>0.8</v>
       </c>
       <c r="AP155">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ155">
         <v>1.45</v>
@@ -33600,7 +33633,7 @@
         <v>1.17</v>
       </c>
       <c r="AP156">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -33728,7 +33761,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -33806,10 +33839,10 @@
         <v>1.17</v>
       </c>
       <c r="AP157">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ157">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR157">
         <v>1.15</v>
@@ -34015,7 +34048,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ158">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR158">
         <v>1.15</v>
@@ -34424,10 +34457,10 @@
         <v>1</v>
       </c>
       <c r="AP160">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ160">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR160">
         <v>1.49</v>
@@ -34552,7 +34585,7 @@
         <v>202</v>
       </c>
       <c r="P161" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q161">
         <v>3.2</v>
@@ -34633,7 +34666,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ161">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34836,7 +34869,7 @@
         <v>1.67</v>
       </c>
       <c r="AP162">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ162">
         <v>2.09</v>
@@ -35042,10 +35075,10 @@
         <v>0.67</v>
       </c>
       <c r="AP163">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ163">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR163">
         <v>1.63</v>
@@ -35170,7 +35203,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35376,7 +35409,7 @@
         <v>101</v>
       </c>
       <c r="P165" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>2.63</v>
@@ -35454,7 +35487,7 @@
         <v>0.57</v>
       </c>
       <c r="AP165">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ165">
         <v>0.75</v>
@@ -35582,7 +35615,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35660,7 +35693,7 @@
         <v>0.57</v>
       </c>
       <c r="AP166">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ166">
         <v>1.08</v>
@@ -35788,7 +35821,7 @@
         <v>205</v>
       </c>
       <c r="P167" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -35866,10 +35899,10 @@
         <v>1.67</v>
       </c>
       <c r="AP167">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ167">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR167">
         <v>1.52</v>
@@ -36075,7 +36108,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ168">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR168">
         <v>1.25</v>
@@ -36200,7 +36233,7 @@
         <v>207</v>
       </c>
       <c r="P169" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q169">
         <v>2.5</v>
@@ -36484,7 +36517,7 @@
         <v>2.29</v>
       </c>
       <c r="AP170">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ170">
         <v>1.71</v>
@@ -36693,7 +36726,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ171">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR171">
         <v>1.56</v>
@@ -36899,7 +36932,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ172">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR172">
         <v>1.32</v>
@@ -37024,7 +37057,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37230,7 +37263,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -37517,7 +37550,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ175">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR175">
         <v>1.45</v>
@@ -37720,7 +37753,7 @@
         <v>1.71</v>
       </c>
       <c r="AP176">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ176">
         <v>1.46</v>
@@ -37926,7 +37959,7 @@
         <v>2</v>
       </c>
       <c r="AP177">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ177">
         <v>1.71</v>
@@ -38260,7 +38293,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -38341,7 +38374,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR179">
         <v>1.29</v>
@@ -38544,10 +38577,10 @@
         <v>1.86</v>
       </c>
       <c r="AP180">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ180">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR180">
         <v>1.26</v>
@@ -38959,7 +38992,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ182">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR182">
         <v>1.19</v>
@@ -39084,7 +39117,7 @@
         <v>214</v>
       </c>
       <c r="P183" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q183">
         <v>3.2</v>
@@ -39162,7 +39195,7 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ183">
         <v>0.71</v>
@@ -39368,7 +39401,7 @@
         <v>0.88</v>
       </c>
       <c r="AP184">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ184">
         <v>0.75</v>
@@ -39496,7 +39529,7 @@
         <v>185</v>
       </c>
       <c r="P185" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q185">
         <v>3.4</v>
@@ -39783,7 +39816,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ186">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR186">
         <v>1.66</v>
@@ -39908,7 +39941,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -39986,7 +40019,7 @@
         <v>0.86</v>
       </c>
       <c r="AP187">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ187">
         <v>0.92</v>
@@ -40195,7 +40228,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ188">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR188">
         <v>1.31</v>
@@ -40401,7 +40434,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ189">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR189">
         <v>1.71</v>
@@ -40526,7 +40559,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40604,10 +40637,10 @@
         <v>0.71</v>
       </c>
       <c r="AP190">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ190">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR190">
         <v>1.22</v>
@@ -40732,7 +40765,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40810,7 +40843,7 @@
         <v>0.86</v>
       </c>
       <c r="AP191">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ191">
         <v>1</v>
@@ -40938,7 +40971,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41016,7 +41049,7 @@
         <v>0.88</v>
       </c>
       <c r="AP192">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ192">
         <v>1.08</v>
@@ -41222,7 +41255,7 @@
         <v>1.57</v>
       </c>
       <c r="AP193">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ193">
         <v>2.09</v>
@@ -41428,10 +41461,10 @@
         <v>1.86</v>
       </c>
       <c r="AP194">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ194">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR194">
         <v>1.51</v>
@@ -41637,7 +41670,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ195">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR195">
         <v>1.49</v>
@@ -41840,10 +41873,10 @@
         <v>1.57</v>
       </c>
       <c r="AP196">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ196">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR196">
         <v>1.37</v>
@@ -41968,7 +42001,7 @@
         <v>221</v>
       </c>
       <c r="P197" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42046,7 +42079,7 @@
         <v>1.29</v>
       </c>
       <c r="AP197">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ197">
         <v>1.58</v>
@@ -42174,7 +42207,7 @@
         <v>101</v>
       </c>
       <c r="P198" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q198">
         <v>3.75</v>
@@ -42380,7 +42413,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42458,10 +42491,10 @@
         <v>1.5</v>
       </c>
       <c r="AP199">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ199">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR199">
         <v>1.51</v>
@@ -42667,7 +42700,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ200">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR200">
         <v>1.45</v>
@@ -42873,7 +42906,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ201">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR201">
         <v>1.27</v>
@@ -42998,7 +43031,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43076,10 +43109,10 @@
         <v>0.78</v>
       </c>
       <c r="AP202">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ202">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR202">
         <v>1.53</v>
@@ -43204,7 +43237,7 @@
         <v>208</v>
       </c>
       <c r="P203" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43285,7 +43318,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ203">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR203">
         <v>1.53</v>
@@ -43410,7 +43443,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -43822,7 +43855,7 @@
         <v>226</v>
       </c>
       <c r="P206" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q206">
         <v>2.85</v>
@@ -43900,7 +43933,7 @@
         <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ206">
         <v>0.92</v>
@@ -44106,7 +44139,7 @@
         <v>1.13</v>
       </c>
       <c r="AP207">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44234,7 +44267,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44440,7 +44473,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44518,10 +44551,10 @@
         <v>1.56</v>
       </c>
       <c r="AP209">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ209">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR209">
         <v>1.49</v>
@@ -44724,7 +44757,7 @@
         <v>1.14</v>
       </c>
       <c r="AP210">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ210">
         <v>1</v>
@@ -44852,7 +44885,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -44933,7 +44966,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ211">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR211">
         <v>1.39</v>
@@ -45136,7 +45169,7 @@
         <v>1.75</v>
       </c>
       <c r="AP212">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ212">
         <v>2.09</v>
@@ -45345,7 +45378,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ213">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR213">
         <v>1.19</v>
@@ -45548,7 +45581,7 @@
         <v>1.13</v>
       </c>
       <c r="AP214">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ214">
         <v>1.5</v>
@@ -45676,7 +45709,7 @@
         <v>234</v>
       </c>
       <c r="P215" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -45757,7 +45790,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ215">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR215">
         <v>1.35</v>
@@ -45963,7 +45996,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ216">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR216">
         <v>1.49</v>
@@ -46088,7 +46121,7 @@
         <v>236</v>
       </c>
       <c r="P217" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46166,7 +46199,7 @@
         <v>1.25</v>
       </c>
       <c r="AP217">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ217">
         <v>1.58</v>
@@ -46294,7 +46327,7 @@
         <v>101</v>
       </c>
       <c r="P218" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46372,7 +46405,7 @@
         <v>1.25</v>
       </c>
       <c r="AP218">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ218">
         <v>1.45</v>
@@ -46578,10 +46611,10 @@
         <v>1.57</v>
       </c>
       <c r="AP219">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ219">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR219">
         <v>1.22</v>
@@ -46706,7 +46739,7 @@
         <v>101</v>
       </c>
       <c r="P220" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46784,7 +46817,7 @@
         <v>1.78</v>
       </c>
       <c r="AP220">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ220">
         <v>1.46</v>
@@ -46990,10 +47023,10 @@
         <v>1.4</v>
       </c>
       <c r="AP221">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ221">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR221">
         <v>1.41</v>
@@ -47118,7 +47151,7 @@
         <v>239</v>
       </c>
       <c r="P222" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Q222">
         <v>2.38</v>
@@ -47402,10 +47435,10 @@
         <v>0.89</v>
       </c>
       <c r="AP223">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ223">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR223">
         <v>1.56</v>
@@ -47608,10 +47641,10 @@
         <v>1.89</v>
       </c>
       <c r="AP224">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ224">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR224">
         <v>1.53</v>
@@ -48020,7 +48053,7 @@
         <v>2</v>
       </c>
       <c r="AP226">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ226">
         <v>1.71</v>
@@ -48148,7 +48181,7 @@
         <v>101</v>
       </c>
       <c r="P227" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48226,10 +48259,10 @@
         <v>1.44</v>
       </c>
       <c r="AP227">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ227">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR227">
         <v>1.42</v>
@@ -48641,7 +48674,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ229">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR229">
         <v>1.66</v>
@@ -48766,7 +48799,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48972,7 +49005,7 @@
         <v>101</v>
       </c>
       <c r="P231" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q231">
         <v>3.4</v>
@@ -49050,10 +49083,10 @@
         <v>1.44</v>
       </c>
       <c r="AP231">
+        <v>1.46</v>
+      </c>
+      <c r="AQ231">
         <v>1.5</v>
-      </c>
-      <c r="AQ231">
-        <v>1.38</v>
       </c>
       <c r="AR231">
         <v>1.28</v>
@@ -49178,7 +49211,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49384,7 +49417,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -49462,10 +49495,10 @@
         <v>0.89</v>
       </c>
       <c r="AP233">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ233">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR233">
         <v>1.21</v>
@@ -49671,7 +49704,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ234">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR234">
         <v>1.16</v>
@@ -49877,7 +49910,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ235">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR235">
         <v>1.41</v>
@@ -50083,7 +50116,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ236">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR236">
         <v>1.36</v>
@@ -50208,7 +50241,7 @@
         <v>244</v>
       </c>
       <c r="P237" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q237">
         <v>4.5</v>
@@ -50289,7 +50322,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ237">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR237">
         <v>1.15</v>
@@ -50414,7 +50447,7 @@
         <v>101</v>
       </c>
       <c r="P238" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q238">
         <v>5.5</v>
@@ -50492,7 +50525,7 @@
         <v>1.89</v>
       </c>
       <c r="AP238">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ238">
         <v>2.09</v>
@@ -50701,7 +50734,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ239">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR239">
         <v>1.85</v>
@@ -50826,7 +50859,7 @@
         <v>246</v>
       </c>
       <c r="P240" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q240">
         <v>2.88</v>
@@ -50904,7 +50937,7 @@
         <v>1.9</v>
       </c>
       <c r="AP240">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ240">
         <v>1.46</v>
@@ -51110,7 +51143,7 @@
         <v>0.89</v>
       </c>
       <c r="AP241">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ241">
         <v>0.75</v>
@@ -51238,7 +51271,7 @@
         <v>101</v>
       </c>
       <c r="P242" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q242">
         <v>3.75</v>
@@ -51316,7 +51349,7 @@
         <v>1.44</v>
       </c>
       <c r="AP242">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ242">
         <v>1.58</v>
@@ -51444,7 +51477,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -51522,7 +51555,7 @@
         <v>1</v>
       </c>
       <c r="AP243">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ243">
         <v>1.5</v>
@@ -51934,10 +51967,10 @@
         <v>1.7</v>
       </c>
       <c r="AP245">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ245">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR245">
         <v>1.53</v>
@@ -52140,10 +52173,10 @@
         <v>0.8</v>
       </c>
       <c r="AP246">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ246">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR246">
         <v>1.42</v>
@@ -52268,7 +52301,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -52349,7 +52382,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ247">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR247">
         <v>1.35</v>
@@ -52474,7 +52507,7 @@
         <v>249</v>
       </c>
       <c r="P248" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q248">
         <v>2.38</v>
@@ -52552,7 +52585,7 @@
         <v>0.9</v>
       </c>
       <c r="AP248">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ248">
         <v>1</v>
@@ -52761,7 +52794,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ249">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR249">
         <v>1.32</v>
@@ -52967,7 +53000,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ250">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR250">
         <v>1.29</v>
@@ -53092,7 +53125,7 @@
         <v>101</v>
       </c>
       <c r="P251" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q251">
         <v>2.5</v>
@@ -53170,7 +53203,7 @@
         <v>1</v>
       </c>
       <c r="AP251">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ251">
         <v>1.08</v>
@@ -53710,7 +53743,7 @@
         <v>254</v>
       </c>
       <c r="P254" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q254">
         <v>2.25</v>
@@ -53788,7 +53821,7 @@
         <v>0.73</v>
       </c>
       <c r="AP254">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ254">
         <v>0.71</v>
@@ -53916,7 +53949,7 @@
         <v>255</v>
       </c>
       <c r="P255" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q255">
         <v>2.1</v>
@@ -53994,10 +54027,10 @@
         <v>0.82</v>
       </c>
       <c r="AP255">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ255">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR255">
         <v>1.47</v>
@@ -54122,7 +54155,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -54200,7 +54233,7 @@
         <v>0.75</v>
       </c>
       <c r="AP256">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ256">
         <v>0.71</v>
@@ -54406,7 +54439,7 @@
         <v>0.8</v>
       </c>
       <c r="AP257">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ257">
         <v>0.92</v>
@@ -54612,10 +54645,10 @@
         <v>0.75</v>
       </c>
       <c r="AP258">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ258">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR258">
         <v>1.51</v>
@@ -54818,7 +54851,7 @@
         <v>1.75</v>
       </c>
       <c r="AP259">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ259">
         <v>1.71</v>
@@ -55027,7 +55060,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ260">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR260">
         <v>1.44</v>
@@ -55230,7 +55263,7 @@
         <v>1.17</v>
       </c>
       <c r="AP261">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ261">
         <v>1.08</v>
@@ -55358,7 +55391,7 @@
         <v>259</v>
       </c>
       <c r="P262" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q262">
         <v>3.6</v>
@@ -55439,7 +55472,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ262">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR262">
         <v>1.31</v>
@@ -55851,7 +55884,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ264">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR264">
         <v>1.35</v>
@@ -56057,7 +56090,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ265">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR265">
         <v>1.41</v>
@@ -56263,7 +56296,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ266">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR266">
         <v>1.65</v>
@@ -56466,7 +56499,7 @@
         <v>1.1</v>
       </c>
       <c r="AP267">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ267">
         <v>1</v>
@@ -56594,7 +56627,7 @@
         <v>101</v>
       </c>
       <c r="P268" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -56672,7 +56705,7 @@
         <v>1.2</v>
       </c>
       <c r="AP268">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ268">
         <v>1.5</v>
@@ -56800,7 +56833,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q269">
         <v>2.4</v>
@@ -56881,7 +56914,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ269">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR269">
         <v>1.45</v>
@@ -57006,7 +57039,7 @@
         <v>184</v>
       </c>
       <c r="P270" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q270">
         <v>3.25</v>
@@ -57290,10 +57323,10 @@
         <v>0.8</v>
       </c>
       <c r="AP271">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ271">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR271">
         <v>1.29</v>
@@ -57418,7 +57451,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57496,10 +57529,10 @@
         <v>1</v>
       </c>
       <c r="AP272">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ272">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR272">
         <v>1.26</v>
@@ -57624,7 +57657,7 @@
         <v>264</v>
       </c>
       <c r="P273" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q273">
         <v>2.75</v>
@@ -57908,10 +57941,10 @@
         <v>0.9</v>
       </c>
       <c r="AP274">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ274">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR274">
         <v>1.16</v>
@@ -58036,7 +58069,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q275">
         <v>2.88</v>
@@ -58117,7 +58150,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ275">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR275">
         <v>1.46</v>
@@ -58242,7 +58275,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Q276">
         <v>3.1</v>
@@ -58320,7 +58353,7 @@
         <v>1.73</v>
       </c>
       <c r="AP276">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ276">
         <v>1.46</v>
@@ -58448,7 +58481,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Q277">
         <v>3.4</v>
@@ -58529,7 +58562,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ277">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR277">
         <v>1.43</v>
@@ -58654,7 +58687,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -58732,7 +58765,7 @@
         <v>1.6</v>
       </c>
       <c r="AP278">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ278">
         <v>1.58</v>
@@ -58860,7 +58893,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -60096,7 +60129,7 @@
         <v>101</v>
       </c>
       <c r="P285" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60302,7 +60335,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="Q286">
         <v>2.6</v>
@@ -60508,7 +60541,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -60792,10 +60825,10 @@
         <v>0.73</v>
       </c>
       <c r="AP288">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ288">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR288">
         <v>1.53</v>
@@ -60998,10 +61031,10 @@
         <v>1.42</v>
       </c>
       <c r="AP289">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ289">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR289">
         <v>1.31</v>
@@ -61077,6 +61110,2478 @@
       </c>
       <c r="BP289">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7476861</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45674.69791666666</v>
+      </c>
+      <c r="F290">
+        <v>27</v>
+      </c>
+      <c r="G290" t="s">
+        <v>77</v>
+      </c>
+      <c r="H290" t="s">
+        <v>73</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>1</v>
+      </c>
+      <c r="L290">
+        <v>2</v>
+      </c>
+      <c r="M290">
+        <v>0</v>
+      </c>
+      <c r="N290">
+        <v>2</v>
+      </c>
+      <c r="O290" t="s">
+        <v>272</v>
+      </c>
+      <c r="P290" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q290">
+        <v>3.75</v>
+      </c>
+      <c r="R290">
+        <v>2.05</v>
+      </c>
+      <c r="S290">
+        <v>3.1</v>
+      </c>
+      <c r="T290">
+        <v>1.44</v>
+      </c>
+      <c r="U290">
+        <v>2.63</v>
+      </c>
+      <c r="V290">
+        <v>3.25</v>
+      </c>
+      <c r="W290">
+        <v>1.33</v>
+      </c>
+      <c r="X290">
+        <v>10</v>
+      </c>
+      <c r="Y290">
+        <v>1.06</v>
+      </c>
+      <c r="Z290">
+        <v>3.15</v>
+      </c>
+      <c r="AA290">
+        <v>3.2</v>
+      </c>
+      <c r="AB290">
+        <v>2.26</v>
+      </c>
+      <c r="AC290">
+        <v>1.07</v>
+      </c>
+      <c r="AD290">
+        <v>8</v>
+      </c>
+      <c r="AE290">
+        <v>1.36</v>
+      </c>
+      <c r="AF290">
+        <v>3.1</v>
+      </c>
+      <c r="AG290">
+        <v>2</v>
+      </c>
+      <c r="AH290">
+        <v>1.73</v>
+      </c>
+      <c r="AI290">
+        <v>1.83</v>
+      </c>
+      <c r="AJ290">
+        <v>1.83</v>
+      </c>
+      <c r="AK290">
+        <v>1.57</v>
+      </c>
+      <c r="AL290">
+        <v>1.28</v>
+      </c>
+      <c r="AM290">
+        <v>1.36</v>
+      </c>
+      <c r="AN290">
+        <v>1</v>
+      </c>
+      <c r="AO290">
+        <v>0.91</v>
+      </c>
+      <c r="AP290">
+        <v>1.15</v>
+      </c>
+      <c r="AQ290">
+        <v>0.83</v>
+      </c>
+      <c r="AR290">
+        <v>1.09</v>
+      </c>
+      <c r="AS290">
+        <v>1.15</v>
+      </c>
+      <c r="AT290">
+        <v>2.24</v>
+      </c>
+      <c r="AU290">
+        <v>3</v>
+      </c>
+      <c r="AV290">
+        <v>4</v>
+      </c>
+      <c r="AW290">
+        <v>3</v>
+      </c>
+      <c r="AX290">
+        <v>1</v>
+      </c>
+      <c r="AY290">
+        <v>13</v>
+      </c>
+      <c r="AZ290">
+        <v>6</v>
+      </c>
+      <c r="BA290">
+        <v>9</v>
+      </c>
+      <c r="BB290">
+        <v>5</v>
+      </c>
+      <c r="BC290">
+        <v>14</v>
+      </c>
+      <c r="BD290">
+        <v>2.17</v>
+      </c>
+      <c r="BE290">
+        <v>6.25</v>
+      </c>
+      <c r="BF290">
+        <v>1.84</v>
+      </c>
+      <c r="BG290">
+        <v>1.42</v>
+      </c>
+      <c r="BH290">
+        <v>2.65</v>
+      </c>
+      <c r="BI290">
+        <v>1.72</v>
+      </c>
+      <c r="BJ290">
+        <v>1.98</v>
+      </c>
+      <c r="BK290">
+        <v>2.15</v>
+      </c>
+      <c r="BL290">
+        <v>1.61</v>
+      </c>
+      <c r="BM290">
+        <v>2.8</v>
+      </c>
+      <c r="BN290">
+        <v>1.38</v>
+      </c>
+      <c r="BO290">
+        <v>3.65</v>
+      </c>
+      <c r="BP290">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="291" spans="1:68">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>7476859</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" t="s">
+        <v>69</v>
+      </c>
+      <c r="E291" s="2">
+        <v>45675.39583333334</v>
+      </c>
+      <c r="F291">
+        <v>27</v>
+      </c>
+      <c r="G291" t="s">
+        <v>76</v>
+      </c>
+      <c r="H291" t="s">
+        <v>74</v>
+      </c>
+      <c r="I291">
+        <v>0</v>
+      </c>
+      <c r="J291">
+        <v>1</v>
+      </c>
+      <c r="K291">
+        <v>1</v>
+      </c>
+      <c r="L291">
+        <v>0</v>
+      </c>
+      <c r="M291">
+        <v>1</v>
+      </c>
+      <c r="N291">
+        <v>1</v>
+      </c>
+      <c r="O291" t="s">
+        <v>101</v>
+      </c>
+      <c r="P291" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q291">
+        <v>4</v>
+      </c>
+      <c r="R291">
+        <v>2.1</v>
+      </c>
+      <c r="S291">
+        <v>2.88</v>
+      </c>
+      <c r="T291">
+        <v>1.44</v>
+      </c>
+      <c r="U291">
+        <v>2.63</v>
+      </c>
+      <c r="V291">
+        <v>3.25</v>
+      </c>
+      <c r="W291">
+        <v>1.33</v>
+      </c>
+      <c r="X291">
+        <v>9</v>
+      </c>
+      <c r="Y291">
+        <v>1.07</v>
+      </c>
+      <c r="Z291">
+        <v>3.03</v>
+      </c>
+      <c r="AA291">
+        <v>3.07</v>
+      </c>
+      <c r="AB291">
+        <v>2.06</v>
+      </c>
+      <c r="AC291">
+        <v>1.07</v>
+      </c>
+      <c r="AD291">
+        <v>8</v>
+      </c>
+      <c r="AE291">
+        <v>1.36</v>
+      </c>
+      <c r="AF291">
+        <v>3.1</v>
+      </c>
+      <c r="AG291">
+        <v>1.98</v>
+      </c>
+      <c r="AH291">
+        <v>1.74</v>
+      </c>
+      <c r="AI291">
+        <v>1.8</v>
+      </c>
+      <c r="AJ291">
+        <v>1.91</v>
+      </c>
+      <c r="AK291">
+        <v>1.7</v>
+      </c>
+      <c r="AL291">
+        <v>1.28</v>
+      </c>
+      <c r="AM291">
+        <v>1.28</v>
+      </c>
+      <c r="AN291">
+        <v>1.58</v>
+      </c>
+      <c r="AO291">
+        <v>1.5</v>
+      </c>
+      <c r="AP291">
+        <v>1.46</v>
+      </c>
+      <c r="AQ291">
+        <v>1.62</v>
+      </c>
+      <c r="AR291">
+        <v>1.25</v>
+      </c>
+      <c r="AS291">
+        <v>1.35</v>
+      </c>
+      <c r="AT291">
+        <v>2.6</v>
+      </c>
+      <c r="AU291">
+        <v>3</v>
+      </c>
+      <c r="AV291">
+        <v>5</v>
+      </c>
+      <c r="AW291">
+        <v>13</v>
+      </c>
+      <c r="AX291">
+        <v>9</v>
+      </c>
+      <c r="AY291">
+        <v>21</v>
+      </c>
+      <c r="AZ291">
+        <v>17</v>
+      </c>
+      <c r="BA291">
+        <v>3</v>
+      </c>
+      <c r="BB291">
+        <v>6</v>
+      </c>
+      <c r="BC291">
+        <v>9</v>
+      </c>
+      <c r="BD291">
+        <v>2.32</v>
+      </c>
+      <c r="BE291">
+        <v>6.4</v>
+      </c>
+      <c r="BF291">
+        <v>1.75</v>
+      </c>
+      <c r="BG291">
+        <v>1.43</v>
+      </c>
+      <c r="BH291">
+        <v>2.55</v>
+      </c>
+      <c r="BI291">
+        <v>1.72</v>
+      </c>
+      <c r="BJ291">
+        <v>1.98</v>
+      </c>
+      <c r="BK291">
+        <v>2.15</v>
+      </c>
+      <c r="BL291">
+        <v>1.61</v>
+      </c>
+      <c r="BM291">
+        <v>2.75</v>
+      </c>
+      <c r="BN291">
+        <v>1.38</v>
+      </c>
+      <c r="BO291">
+        <v>3.65</v>
+      </c>
+      <c r="BP291">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="292" spans="1:68">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>7476858</v>
+      </c>
+      <c r="C292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D292" t="s">
+        <v>69</v>
+      </c>
+      <c r="E292" s="2">
+        <v>45675.39583333334</v>
+      </c>
+      <c r="F292">
+        <v>27</v>
+      </c>
+      <c r="G292" t="s">
+        <v>82</v>
+      </c>
+      <c r="H292" t="s">
+        <v>92</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>0</v>
+      </c>
+      <c r="L292">
+        <v>0</v>
+      </c>
+      <c r="M292">
+        <v>1</v>
+      </c>
+      <c r="N292">
+        <v>1</v>
+      </c>
+      <c r="O292" t="s">
+        <v>101</v>
+      </c>
+      <c r="P292" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q292">
+        <v>4</v>
+      </c>
+      <c r="R292">
+        <v>2.1</v>
+      </c>
+      <c r="S292">
+        <v>2.88</v>
+      </c>
+      <c r="T292">
+        <v>1.44</v>
+      </c>
+      <c r="U292">
+        <v>2.63</v>
+      </c>
+      <c r="V292">
+        <v>3.25</v>
+      </c>
+      <c r="W292">
+        <v>1.33</v>
+      </c>
+      <c r="X292">
+        <v>9</v>
+      </c>
+      <c r="Y292">
+        <v>1.07</v>
+      </c>
+      <c r="Z292">
+        <v>3.11</v>
+      </c>
+      <c r="AA292">
+        <v>3.05</v>
+      </c>
+      <c r="AB292">
+        <v>2.03</v>
+      </c>
+      <c r="AC292">
+        <v>1.05</v>
+      </c>
+      <c r="AD292">
+        <v>10</v>
+      </c>
+      <c r="AE292">
+        <v>1.33</v>
+      </c>
+      <c r="AF292">
+        <v>3.25</v>
+      </c>
+      <c r="AG292">
+        <v>2</v>
+      </c>
+      <c r="AH292">
+        <v>1.72</v>
+      </c>
+      <c r="AI292">
+        <v>1.83</v>
+      </c>
+      <c r="AJ292">
+        <v>1.83</v>
+      </c>
+      <c r="AK292">
+        <v>1.72</v>
+      </c>
+      <c r="AL292">
+        <v>1.25</v>
+      </c>
+      <c r="AM292">
+        <v>1.33</v>
+      </c>
+      <c r="AN292">
+        <v>0.75</v>
+      </c>
+      <c r="AO292">
+        <v>0.92</v>
+      </c>
+      <c r="AP292">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ292">
+        <v>1.08</v>
+      </c>
+      <c r="AR292">
+        <v>1.32</v>
+      </c>
+      <c r="AS292">
+        <v>1.27</v>
+      </c>
+      <c r="AT292">
+        <v>2.59</v>
+      </c>
+      <c r="AU292">
+        <v>3</v>
+      </c>
+      <c r="AV292">
+        <v>3</v>
+      </c>
+      <c r="AW292">
+        <v>6</v>
+      </c>
+      <c r="AX292">
+        <v>6</v>
+      </c>
+      <c r="AY292">
+        <v>13</v>
+      </c>
+      <c r="AZ292">
+        <v>10</v>
+      </c>
+      <c r="BA292">
+        <v>6</v>
+      </c>
+      <c r="BB292">
+        <v>4</v>
+      </c>
+      <c r="BC292">
+        <v>10</v>
+      </c>
+      <c r="BD292">
+        <v>2.02</v>
+      </c>
+      <c r="BE292">
+        <v>6.75</v>
+      </c>
+      <c r="BF292">
+        <v>1.95</v>
+      </c>
+      <c r="BG292">
+        <v>1.22</v>
+      </c>
+      <c r="BH292">
+        <v>3.8</v>
+      </c>
+      <c r="BI292">
+        <v>1.38</v>
+      </c>
+      <c r="BJ292">
+        <v>2.75</v>
+      </c>
+      <c r="BK292">
+        <v>1.63</v>
+      </c>
+      <c r="BL292">
+        <v>2.12</v>
+      </c>
+      <c r="BM292">
+        <v>1.97</v>
+      </c>
+      <c r="BN292">
+        <v>1.74</v>
+      </c>
+      <c r="BO292">
+        <v>2.43</v>
+      </c>
+      <c r="BP292">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="293" spans="1:68">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>7476863</v>
+      </c>
+      <c r="C293" t="s">
+        <v>68</v>
+      </c>
+      <c r="D293" t="s">
+        <v>69</v>
+      </c>
+      <c r="E293" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F293">
+        <v>27</v>
+      </c>
+      <c r="G293" t="s">
+        <v>90</v>
+      </c>
+      <c r="H293" t="s">
+        <v>89</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293">
+        <v>2</v>
+      </c>
+      <c r="K293">
+        <v>3</v>
+      </c>
+      <c r="L293">
+        <v>3</v>
+      </c>
+      <c r="M293">
+        <v>2</v>
+      </c>
+      <c r="N293">
+        <v>5</v>
+      </c>
+      <c r="O293" t="s">
+        <v>273</v>
+      </c>
+      <c r="P293" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q293">
+        <v>2</v>
+      </c>
+      <c r="R293">
+        <v>2.38</v>
+      </c>
+      <c r="S293">
+        <v>6.5</v>
+      </c>
+      <c r="T293">
+        <v>1.36</v>
+      </c>
+      <c r="U293">
+        <v>3</v>
+      </c>
+      <c r="V293">
+        <v>2.63</v>
+      </c>
+      <c r="W293">
+        <v>1.44</v>
+      </c>
+      <c r="X293">
+        <v>7</v>
+      </c>
+      <c r="Y293">
+        <v>1.1</v>
+      </c>
+      <c r="Z293">
+        <v>1.39</v>
+      </c>
+      <c r="AA293">
+        <v>3.91</v>
+      </c>
+      <c r="AB293">
+        <v>5.9</v>
+      </c>
+      <c r="AC293">
+        <v>1.03</v>
+      </c>
+      <c r="AD293">
+        <v>13</v>
+      </c>
+      <c r="AE293">
+        <v>1.25</v>
+      </c>
+      <c r="AF293">
+        <v>3.75</v>
+      </c>
+      <c r="AG293">
+        <v>1.8</v>
+      </c>
+      <c r="AH293">
+        <v>2</v>
+      </c>
+      <c r="AI293">
+        <v>1.83</v>
+      </c>
+      <c r="AJ293">
+        <v>1.83</v>
+      </c>
+      <c r="AK293">
+        <v>1.11</v>
+      </c>
+      <c r="AL293">
+        <v>1.17</v>
+      </c>
+      <c r="AM293">
+        <v>2.7</v>
+      </c>
+      <c r="AN293">
+        <v>1.55</v>
+      </c>
+      <c r="AO293">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP293">
+        <v>1.67</v>
+      </c>
+      <c r="AQ293">
+        <v>0.64</v>
+      </c>
+      <c r="AR293">
+        <v>1.19</v>
+      </c>
+      <c r="AS293">
+        <v>0.83</v>
+      </c>
+      <c r="AT293">
+        <v>2.02</v>
+      </c>
+      <c r="AU293">
+        <v>11</v>
+      </c>
+      <c r="AV293">
+        <v>5</v>
+      </c>
+      <c r="AW293">
+        <v>12</v>
+      </c>
+      <c r="AX293">
+        <v>8</v>
+      </c>
+      <c r="AY293">
+        <v>28</v>
+      </c>
+      <c r="AZ293">
+        <v>16</v>
+      </c>
+      <c r="BA293">
+        <v>9</v>
+      </c>
+      <c r="BB293">
+        <v>6</v>
+      </c>
+      <c r="BC293">
+        <v>15</v>
+      </c>
+      <c r="BD293">
+        <v>1.38</v>
+      </c>
+      <c r="BE293">
+        <v>6.75</v>
+      </c>
+      <c r="BF293">
+        <v>3.45</v>
+      </c>
+      <c r="BG293">
+        <v>1.38</v>
+      </c>
+      <c r="BH293">
+        <v>2.7</v>
+      </c>
+      <c r="BI293">
+        <v>1.67</v>
+      </c>
+      <c r="BJ293">
+        <v>2.07</v>
+      </c>
+      <c r="BK293">
+        <v>2.07</v>
+      </c>
+      <c r="BL293">
+        <v>1.67</v>
+      </c>
+      <c r="BM293">
+        <v>2.65</v>
+      </c>
+      <c r="BN293">
+        <v>1.42</v>
+      </c>
+      <c r="BO293">
+        <v>3.4</v>
+      </c>
+      <c r="BP293">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="294" spans="1:68">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>7476857</v>
+      </c>
+      <c r="C294" t="s">
+        <v>68</v>
+      </c>
+      <c r="D294" t="s">
+        <v>69</v>
+      </c>
+      <c r="E294" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F294">
+        <v>27</v>
+      </c>
+      <c r="G294" t="s">
+        <v>83</v>
+      </c>
+      <c r="H294" t="s">
+        <v>85</v>
+      </c>
+      <c r="I294">
+        <v>0</v>
+      </c>
+      <c r="J294">
+        <v>1</v>
+      </c>
+      <c r="K294">
+        <v>1</v>
+      </c>
+      <c r="L294">
+        <v>0</v>
+      </c>
+      <c r="M294">
+        <v>1</v>
+      </c>
+      <c r="N294">
+        <v>1</v>
+      </c>
+      <c r="O294" t="s">
+        <v>101</v>
+      </c>
+      <c r="P294" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q294">
+        <v>2.88</v>
+      </c>
+      <c r="R294">
+        <v>2.1</v>
+      </c>
+      <c r="S294">
+        <v>3.75</v>
+      </c>
+      <c r="T294">
+        <v>1.4</v>
+      </c>
+      <c r="U294">
+        <v>2.75</v>
+      </c>
+      <c r="V294">
+        <v>3</v>
+      </c>
+      <c r="W294">
+        <v>1.36</v>
+      </c>
+      <c r="X294">
+        <v>8</v>
+      </c>
+      <c r="Y294">
+        <v>1.08</v>
+      </c>
+      <c r="Z294">
+        <v>2.2</v>
+      </c>
+      <c r="AA294">
+        <v>3.25</v>
+      </c>
+      <c r="AB294">
+        <v>3.2</v>
+      </c>
+      <c r="AC294">
+        <v>1.06</v>
+      </c>
+      <c r="AD294">
+        <v>8.5</v>
+      </c>
+      <c r="AE294">
+        <v>1.33</v>
+      </c>
+      <c r="AF294">
+        <v>3.25</v>
+      </c>
+      <c r="AG294">
+        <v>1.9</v>
+      </c>
+      <c r="AH294">
+        <v>1.8</v>
+      </c>
+      <c r="AI294">
+        <v>1.73</v>
+      </c>
+      <c r="AJ294">
+        <v>2</v>
+      </c>
+      <c r="AK294">
+        <v>1.33</v>
+      </c>
+      <c r="AL294">
+        <v>1.28</v>
+      </c>
+      <c r="AM294">
+        <v>1.65</v>
+      </c>
+      <c r="AN294">
+        <v>1.25</v>
+      </c>
+      <c r="AO294">
+        <v>0.91</v>
+      </c>
+      <c r="AP294">
+        <v>1.15</v>
+      </c>
+      <c r="AQ294">
+        <v>1.08</v>
+      </c>
+      <c r="AR294">
+        <v>1.46</v>
+      </c>
+      <c r="AS294">
+        <v>1.04</v>
+      </c>
+      <c r="AT294">
+        <v>2.5</v>
+      </c>
+      <c r="AU294">
+        <v>2</v>
+      </c>
+      <c r="AV294">
+        <v>6</v>
+      </c>
+      <c r="AW294">
+        <v>14</v>
+      </c>
+      <c r="AX294">
+        <v>4</v>
+      </c>
+      <c r="AY294">
+        <v>20</v>
+      </c>
+      <c r="AZ294">
+        <v>12</v>
+      </c>
+      <c r="BA294">
+        <v>8</v>
+      </c>
+      <c r="BB294">
+        <v>4</v>
+      </c>
+      <c r="BC294">
+        <v>12</v>
+      </c>
+      <c r="BD294">
+        <v>1.75</v>
+      </c>
+      <c r="BE294">
+        <v>6.75</v>
+      </c>
+      <c r="BF294">
+        <v>2.3</v>
+      </c>
+      <c r="BG294">
+        <v>1.3</v>
+      </c>
+      <c r="BH294">
+        <v>3.15</v>
+      </c>
+      <c r="BI294">
+        <v>1.52</v>
+      </c>
+      <c r="BJ294">
+        <v>2.33</v>
+      </c>
+      <c r="BK294">
+        <v>1.85</v>
+      </c>
+      <c r="BL294">
+        <v>1.83</v>
+      </c>
+      <c r="BM294">
+        <v>2.33</v>
+      </c>
+      <c r="BN294">
+        <v>1.52</v>
+      </c>
+      <c r="BO294">
+        <v>2.95</v>
+      </c>
+      <c r="BP294">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="295" spans="1:68">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>7476860</v>
+      </c>
+      <c r="C295" t="s">
+        <v>68</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F295">
+        <v>27</v>
+      </c>
+      <c r="G295" t="s">
+        <v>87</v>
+      </c>
+      <c r="H295" t="s">
+        <v>70</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+      <c r="J295">
+        <v>1</v>
+      </c>
+      <c r="K295">
+        <v>2</v>
+      </c>
+      <c r="L295">
+        <v>1</v>
+      </c>
+      <c r="M295">
+        <v>1</v>
+      </c>
+      <c r="N295">
+        <v>2</v>
+      </c>
+      <c r="O295" t="s">
+        <v>163</v>
+      </c>
+      <c r="P295" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q295">
+        <v>3.4</v>
+      </c>
+      <c r="R295">
+        <v>2.2</v>
+      </c>
+      <c r="S295">
+        <v>3</v>
+      </c>
+      <c r="T295">
+        <v>1.36</v>
+      </c>
+      <c r="U295">
+        <v>3</v>
+      </c>
+      <c r="V295">
+        <v>2.63</v>
+      </c>
+      <c r="W295">
+        <v>1.44</v>
+      </c>
+      <c r="X295">
+        <v>7</v>
+      </c>
+      <c r="Y295">
+        <v>1.1</v>
+      </c>
+      <c r="Z295">
+        <v>2.62</v>
+      </c>
+      <c r="AA295">
+        <v>3.1</v>
+      </c>
+      <c r="AB295">
+        <v>2.29</v>
+      </c>
+      <c r="AC295">
+        <v>1.04</v>
+      </c>
+      <c r="AD295">
+        <v>13</v>
+      </c>
+      <c r="AE295">
+        <v>1.25</v>
+      </c>
+      <c r="AF295">
+        <v>3.75</v>
+      </c>
+      <c r="AG295">
+        <v>1.8</v>
+      </c>
+      <c r="AH295">
+        <v>2</v>
+      </c>
+      <c r="AI295">
+        <v>1.62</v>
+      </c>
+      <c r="AJ295">
+        <v>2.2</v>
+      </c>
+      <c r="AK295">
+        <v>1.55</v>
+      </c>
+      <c r="AL295">
+        <v>1.25</v>
+      </c>
+      <c r="AM295">
+        <v>1.45</v>
+      </c>
+      <c r="AN295">
+        <v>1.5</v>
+      </c>
+      <c r="AO295">
+        <v>1.33</v>
+      </c>
+      <c r="AP295">
+        <v>1.46</v>
+      </c>
+      <c r="AQ295">
+        <v>1.31</v>
+      </c>
+      <c r="AR295">
+        <v>1.29</v>
+      </c>
+      <c r="AS295">
+        <v>1.27</v>
+      </c>
+      <c r="AT295">
+        <v>2.56</v>
+      </c>
+      <c r="AU295">
+        <v>4</v>
+      </c>
+      <c r="AV295">
+        <v>3</v>
+      </c>
+      <c r="AW295">
+        <v>6</v>
+      </c>
+      <c r="AX295">
+        <v>7</v>
+      </c>
+      <c r="AY295">
+        <v>14</v>
+      </c>
+      <c r="AZ295">
+        <v>11</v>
+      </c>
+      <c r="BA295">
+        <v>4</v>
+      </c>
+      <c r="BB295">
+        <v>11</v>
+      </c>
+      <c r="BC295">
+        <v>15</v>
+      </c>
+      <c r="BD295">
+        <v>2.15</v>
+      </c>
+      <c r="BE295">
+        <v>6.4</v>
+      </c>
+      <c r="BF295">
+        <v>1.88</v>
+      </c>
+      <c r="BG295">
+        <v>1.38</v>
+      </c>
+      <c r="BH295">
+        <v>2.8</v>
+      </c>
+      <c r="BI295">
+        <v>1.64</v>
+      </c>
+      <c r="BJ295">
+        <v>2.1</v>
+      </c>
+      <c r="BK295">
+        <v>2.02</v>
+      </c>
+      <c r="BL295">
+        <v>1.7</v>
+      </c>
+      <c r="BM295">
+        <v>2.55</v>
+      </c>
+      <c r="BN295">
+        <v>1.44</v>
+      </c>
+      <c r="BO295">
+        <v>3.4</v>
+      </c>
+      <c r="BP295">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="296" spans="1:68">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>7476864</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F296">
+        <v>27</v>
+      </c>
+      <c r="G296" t="s">
+        <v>79</v>
+      </c>
+      <c r="H296" t="s">
+        <v>75</v>
+      </c>
+      <c r="I296">
+        <v>0</v>
+      </c>
+      <c r="J296">
+        <v>2</v>
+      </c>
+      <c r="K296">
+        <v>2</v>
+      </c>
+      <c r="L296">
+        <v>0</v>
+      </c>
+      <c r="M296">
+        <v>2</v>
+      </c>
+      <c r="N296">
+        <v>2</v>
+      </c>
+      <c r="O296" t="s">
+        <v>101</v>
+      </c>
+      <c r="P296" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q296">
+        <v>2.75</v>
+      </c>
+      <c r="R296">
+        <v>2.1</v>
+      </c>
+      <c r="S296">
+        <v>4</v>
+      </c>
+      <c r="T296">
+        <v>1.4</v>
+      </c>
+      <c r="U296">
+        <v>2.75</v>
+      </c>
+      <c r="V296">
+        <v>3</v>
+      </c>
+      <c r="W296">
+        <v>1.36</v>
+      </c>
+      <c r="X296">
+        <v>9</v>
+      </c>
+      <c r="Y296">
+        <v>1.07</v>
+      </c>
+      <c r="Z296">
+        <v>2.02</v>
+      </c>
+      <c r="AA296">
+        <v>2.97</v>
+      </c>
+      <c r="AB296">
+        <v>3.23</v>
+      </c>
+      <c r="AC296">
+        <v>1.07</v>
+      </c>
+      <c r="AD296">
+        <v>8</v>
+      </c>
+      <c r="AE296">
+        <v>1.35</v>
+      </c>
+      <c r="AF296">
+        <v>3.1</v>
+      </c>
+      <c r="AG296">
+        <v>2</v>
+      </c>
+      <c r="AH296">
+        <v>1.72</v>
+      </c>
+      <c r="AI296">
+        <v>1.8</v>
+      </c>
+      <c r="AJ296">
+        <v>1.91</v>
+      </c>
+      <c r="AK296">
+        <v>1.25</v>
+      </c>
+      <c r="AL296">
+        <v>1.25</v>
+      </c>
+      <c r="AM296">
+        <v>1.77</v>
+      </c>
+      <c r="AN296">
+        <v>2</v>
+      </c>
+      <c r="AO296">
+        <v>1.1</v>
+      </c>
+      <c r="AP296">
+        <v>1.85</v>
+      </c>
+      <c r="AQ296">
+        <v>1.27</v>
+      </c>
+      <c r="AR296">
+        <v>1.45</v>
+      </c>
+      <c r="AS296">
+        <v>1.13</v>
+      </c>
+      <c r="AT296">
+        <v>2.58</v>
+      </c>
+      <c r="AU296">
+        <v>5</v>
+      </c>
+      <c r="AV296">
+        <v>4</v>
+      </c>
+      <c r="AW296">
+        <v>8</v>
+      </c>
+      <c r="AX296">
+        <v>8</v>
+      </c>
+      <c r="AY296">
+        <v>14</v>
+      </c>
+      <c r="AZ296">
+        <v>14</v>
+      </c>
+      <c r="BA296">
+        <v>2</v>
+      </c>
+      <c r="BB296">
+        <v>3</v>
+      </c>
+      <c r="BC296">
+        <v>5</v>
+      </c>
+      <c r="BD296">
+        <v>1.6</v>
+      </c>
+      <c r="BE296">
+        <v>6.75</v>
+      </c>
+      <c r="BF296">
+        <v>2.63</v>
+      </c>
+      <c r="BG296">
+        <v>1.3</v>
+      </c>
+      <c r="BH296">
+        <v>3.05</v>
+      </c>
+      <c r="BI296">
+        <v>1.53</v>
+      </c>
+      <c r="BJ296">
+        <v>2.32</v>
+      </c>
+      <c r="BK296">
+        <v>1.85</v>
+      </c>
+      <c r="BL296">
+        <v>1.83</v>
+      </c>
+      <c r="BM296">
+        <v>2.33</v>
+      </c>
+      <c r="BN296">
+        <v>1.52</v>
+      </c>
+      <c r="BO296">
+        <v>2.95</v>
+      </c>
+      <c r="BP296">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="297" spans="1:68">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>7476866</v>
+      </c>
+      <c r="C297" t="s">
+        <v>68</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F297">
+        <v>27</v>
+      </c>
+      <c r="G297" t="s">
+        <v>81</v>
+      </c>
+      <c r="H297" t="s">
+        <v>78</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+      <c r="J297">
+        <v>1</v>
+      </c>
+      <c r="K297">
+        <v>2</v>
+      </c>
+      <c r="L297">
+        <v>4</v>
+      </c>
+      <c r="M297">
+        <v>2</v>
+      </c>
+      <c r="N297">
+        <v>6</v>
+      </c>
+      <c r="O297" t="s">
+        <v>274</v>
+      </c>
+      <c r="P297" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q297">
+        <v>2.38</v>
+      </c>
+      <c r="R297">
+        <v>2.25</v>
+      </c>
+      <c r="S297">
+        <v>4.75</v>
+      </c>
+      <c r="T297">
+        <v>1.36</v>
+      </c>
+      <c r="U297">
+        <v>3</v>
+      </c>
+      <c r="V297">
+        <v>2.63</v>
+      </c>
+      <c r="W297">
+        <v>1.44</v>
+      </c>
+      <c r="X297">
+        <v>7</v>
+      </c>
+      <c r="Y297">
+        <v>1.1</v>
+      </c>
+      <c r="Z297">
+        <v>1.84</v>
+      </c>
+      <c r="AA297">
+        <v>3.08</v>
+      </c>
+      <c r="AB297">
+        <v>3.34</v>
+      </c>
+      <c r="AC297">
+        <v>1.05</v>
+      </c>
+      <c r="AD297">
+        <v>9.5</v>
+      </c>
+      <c r="AE297">
+        <v>1.25</v>
+      </c>
+      <c r="AF297">
+        <v>3.8</v>
+      </c>
+      <c r="AG297">
+        <v>1.81</v>
+      </c>
+      <c r="AH297">
+        <v>1.95</v>
+      </c>
+      <c r="AI297">
+        <v>1.73</v>
+      </c>
+      <c r="AJ297">
+        <v>2</v>
+      </c>
+      <c r="AK297">
+        <v>1.2</v>
+      </c>
+      <c r="AL297">
+        <v>1.22</v>
+      </c>
+      <c r="AM297">
+        <v>2</v>
+      </c>
+      <c r="AN297">
+        <v>2.46</v>
+      </c>
+      <c r="AO297">
+        <v>1.44</v>
+      </c>
+      <c r="AP297">
+        <v>2.5</v>
+      </c>
+      <c r="AQ297">
+        <v>1.3</v>
+      </c>
+      <c r="AR297">
+        <v>1.58</v>
+      </c>
+      <c r="AS297">
+        <v>1.48</v>
+      </c>
+      <c r="AT297">
+        <v>3.06</v>
+      </c>
+      <c r="AU297">
+        <v>10</v>
+      </c>
+      <c r="AV297">
+        <v>4</v>
+      </c>
+      <c r="AW297">
+        <v>16</v>
+      </c>
+      <c r="AX297">
+        <v>3</v>
+      </c>
+      <c r="AY297">
+        <v>26</v>
+      </c>
+      <c r="AZ297">
+        <v>7</v>
+      </c>
+      <c r="BA297">
+        <v>8</v>
+      </c>
+      <c r="BB297">
+        <v>2</v>
+      </c>
+      <c r="BC297">
+        <v>10</v>
+      </c>
+      <c r="BD297">
+        <v>1.65</v>
+      </c>
+      <c r="BE297">
+        <v>6.4</v>
+      </c>
+      <c r="BF297">
+        <v>2.48</v>
+      </c>
+      <c r="BG297">
+        <v>1.38</v>
+      </c>
+      <c r="BH297">
+        <v>2.75</v>
+      </c>
+      <c r="BI297">
+        <v>1.65</v>
+      </c>
+      <c r="BJ297">
+        <v>2.08</v>
+      </c>
+      <c r="BK297">
+        <v>2.05</v>
+      </c>
+      <c r="BL297">
+        <v>1.68</v>
+      </c>
+      <c r="BM297">
+        <v>2.63</v>
+      </c>
+      <c r="BN297">
+        <v>1.43</v>
+      </c>
+      <c r="BO297">
+        <v>3.45</v>
+      </c>
+      <c r="BP297">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="298" spans="1:68">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>7476865</v>
+      </c>
+      <c r="C298" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" t="s">
+        <v>69</v>
+      </c>
+      <c r="E298" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F298">
+        <v>27</v>
+      </c>
+      <c r="G298" t="s">
+        <v>91</v>
+      </c>
+      <c r="H298" t="s">
+        <v>72</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>1</v>
+      </c>
+      <c r="L298">
+        <v>2</v>
+      </c>
+      <c r="M298">
+        <v>0</v>
+      </c>
+      <c r="N298">
+        <v>2</v>
+      </c>
+      <c r="O298" t="s">
+        <v>275</v>
+      </c>
+      <c r="P298" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q298">
+        <v>3.4</v>
+      </c>
+      <c r="R298">
+        <v>2.05</v>
+      </c>
+      <c r="S298">
+        <v>3.4</v>
+      </c>
+      <c r="T298">
+        <v>1.44</v>
+      </c>
+      <c r="U298">
+        <v>2.63</v>
+      </c>
+      <c r="V298">
+        <v>3.25</v>
+      </c>
+      <c r="W298">
+        <v>1.33</v>
+      </c>
+      <c r="X298">
+        <v>9</v>
+      </c>
+      <c r="Y298">
+        <v>1.07</v>
+      </c>
+      <c r="Z298">
+        <v>2.46</v>
+      </c>
+      <c r="AA298">
+        <v>2.96</v>
+      </c>
+      <c r="AB298">
+        <v>2.51</v>
+      </c>
+      <c r="AC298">
+        <v>1.07</v>
+      </c>
+      <c r="AD298">
+        <v>8</v>
+      </c>
+      <c r="AE298">
+        <v>1.36</v>
+      </c>
+      <c r="AF298">
+        <v>3.1</v>
+      </c>
+      <c r="AG298">
+        <v>2.03</v>
+      </c>
+      <c r="AH298">
+        <v>1.7</v>
+      </c>
+      <c r="AI298">
+        <v>1.83</v>
+      </c>
+      <c r="AJ298">
+        <v>1.83</v>
+      </c>
+      <c r="AK298">
+        <v>1.45</v>
+      </c>
+      <c r="AL298">
+        <v>1.28</v>
+      </c>
+      <c r="AM298">
+        <v>1.45</v>
+      </c>
+      <c r="AN298">
+        <v>1.25</v>
+      </c>
+      <c r="AO298">
+        <v>0.75</v>
+      </c>
+      <c r="AP298">
+        <v>1.38</v>
+      </c>
+      <c r="AQ298">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR298">
+        <v>1.32</v>
+      </c>
+      <c r="AS298">
+        <v>1.14</v>
+      </c>
+      <c r="AT298">
+        <v>2.46</v>
+      </c>
+      <c r="AU298">
+        <v>5</v>
+      </c>
+      <c r="AV298">
+        <v>3</v>
+      </c>
+      <c r="AW298">
+        <v>10</v>
+      </c>
+      <c r="AX298">
+        <v>5</v>
+      </c>
+      <c r="AY298">
+        <v>18</v>
+      </c>
+      <c r="AZ298">
+        <v>11</v>
+      </c>
+      <c r="BA298">
+        <v>6</v>
+      </c>
+      <c r="BB298">
+        <v>4</v>
+      </c>
+      <c r="BC298">
+        <v>10</v>
+      </c>
+      <c r="BD298">
+        <v>2.05</v>
+      </c>
+      <c r="BE298">
+        <v>6.1</v>
+      </c>
+      <c r="BF298">
+        <v>1.97</v>
+      </c>
+      <c r="BG298">
+        <v>1.42</v>
+      </c>
+      <c r="BH298">
+        <v>2.63</v>
+      </c>
+      <c r="BI298">
+        <v>1.72</v>
+      </c>
+      <c r="BJ298">
+        <v>1.98</v>
+      </c>
+      <c r="BK298">
+        <v>2.15</v>
+      </c>
+      <c r="BL298">
+        <v>1.61</v>
+      </c>
+      <c r="BM298">
+        <v>2.8</v>
+      </c>
+      <c r="BN298">
+        <v>1.38</v>
+      </c>
+      <c r="BO298">
+        <v>3.7</v>
+      </c>
+      <c r="BP298">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="299" spans="1:68">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>7476855</v>
+      </c>
+      <c r="C299" t="s">
+        <v>68</v>
+      </c>
+      <c r="D299" t="s">
+        <v>69</v>
+      </c>
+      <c r="E299" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F299">
+        <v>27</v>
+      </c>
+      <c r="G299" t="s">
+        <v>71</v>
+      </c>
+      <c r="H299" t="s">
+        <v>80</v>
+      </c>
+      <c r="I299">
+        <v>0</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>0</v>
+      </c>
+      <c r="L299">
+        <v>2</v>
+      </c>
+      <c r="M299">
+        <v>0</v>
+      </c>
+      <c r="N299">
+        <v>2</v>
+      </c>
+      <c r="O299" t="s">
+        <v>276</v>
+      </c>
+      <c r="P299" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q299">
+        <v>2.3</v>
+      </c>
+      <c r="R299">
+        <v>2.1</v>
+      </c>
+      <c r="S299">
+        <v>5.5</v>
+      </c>
+      <c r="T299">
+        <v>1.44</v>
+      </c>
+      <c r="U299">
+        <v>2.63</v>
+      </c>
+      <c r="V299">
+        <v>3.25</v>
+      </c>
+      <c r="W299">
+        <v>1.33</v>
+      </c>
+      <c r="X299">
+        <v>9</v>
+      </c>
+      <c r="Y299">
+        <v>1.07</v>
+      </c>
+      <c r="Z299">
+        <v>1.62</v>
+      </c>
+      <c r="AA299">
+        <v>3.32</v>
+      </c>
+      <c r="AB299">
+        <v>4.49</v>
+      </c>
+      <c r="AC299">
+        <v>1.07</v>
+      </c>
+      <c r="AD299">
+        <v>8</v>
+      </c>
+      <c r="AE299">
+        <v>1.38</v>
+      </c>
+      <c r="AF299">
+        <v>3</v>
+      </c>
+      <c r="AG299">
+        <v>2</v>
+      </c>
+      <c r="AH299">
+        <v>1.72</v>
+      </c>
+      <c r="AI299">
+        <v>2</v>
+      </c>
+      <c r="AJ299">
+        <v>1.73</v>
+      </c>
+      <c r="AK299">
+        <v>1.14</v>
+      </c>
+      <c r="AL299">
+        <v>1.22</v>
+      </c>
+      <c r="AM299">
+        <v>2.15</v>
+      </c>
+      <c r="AN299">
+        <v>2</v>
+      </c>
+      <c r="AO299">
+        <v>0.67</v>
+      </c>
+      <c r="AP299">
+        <v>2.08</v>
+      </c>
+      <c r="AQ299">
+        <v>0.62</v>
+      </c>
+      <c r="AR299">
+        <v>1.4</v>
+      </c>
+      <c r="AS299">
+        <v>1.18</v>
+      </c>
+      <c r="AT299">
+        <v>2.58</v>
+      </c>
+      <c r="AU299">
+        <v>6</v>
+      </c>
+      <c r="AV299">
+        <v>3</v>
+      </c>
+      <c r="AW299">
+        <v>3</v>
+      </c>
+      <c r="AX299">
+        <v>10</v>
+      </c>
+      <c r="AY299">
+        <v>11</v>
+      </c>
+      <c r="AZ299">
+        <v>15</v>
+      </c>
+      <c r="BA299">
+        <v>1</v>
+      </c>
+      <c r="BB299">
+        <v>4</v>
+      </c>
+      <c r="BC299">
+        <v>5</v>
+      </c>
+      <c r="BD299">
+        <v>1.52</v>
+      </c>
+      <c r="BE299">
+        <v>6.4</v>
+      </c>
+      <c r="BF299">
+        <v>2.8</v>
+      </c>
+      <c r="BG299">
+        <v>1.37</v>
+      </c>
+      <c r="BH299">
+        <v>2.8</v>
+      </c>
+      <c r="BI299">
+        <v>1.64</v>
+      </c>
+      <c r="BJ299">
+        <v>2.1</v>
+      </c>
+      <c r="BK299">
+        <v>2.02</v>
+      </c>
+      <c r="BL299">
+        <v>1.7</v>
+      </c>
+      <c r="BM299">
+        <v>2.6</v>
+      </c>
+      <c r="BN299">
+        <v>1.43</v>
+      </c>
+      <c r="BO299">
+        <v>3.4</v>
+      </c>
+      <c r="BP299">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="300" spans="1:68">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>7476856</v>
+      </c>
+      <c r="C300" t="s">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>69</v>
+      </c>
+      <c r="E300" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F300">
+        <v>27</v>
+      </c>
+      <c r="G300" t="s">
+        <v>84</v>
+      </c>
+      <c r="H300" t="s">
+        <v>93</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>2</v>
+      </c>
+      <c r="K300">
+        <v>2</v>
+      </c>
+      <c r="L300">
+        <v>0</v>
+      </c>
+      <c r="M300">
+        <v>3</v>
+      </c>
+      <c r="N300">
+        <v>3</v>
+      </c>
+      <c r="O300" t="s">
+        <v>101</v>
+      </c>
+      <c r="P300" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q300">
+        <v>3.6</v>
+      </c>
+      <c r="R300">
+        <v>2.25</v>
+      </c>
+      <c r="S300">
+        <v>2.75</v>
+      </c>
+      <c r="T300">
+        <v>1.36</v>
+      </c>
+      <c r="U300">
+        <v>3</v>
+      </c>
+      <c r="V300">
+        <v>2.63</v>
+      </c>
+      <c r="W300">
+        <v>1.44</v>
+      </c>
+      <c r="X300">
+        <v>7</v>
+      </c>
+      <c r="Y300">
+        <v>1.1</v>
+      </c>
+      <c r="Z300">
+        <v>2.74</v>
+      </c>
+      <c r="AA300">
+        <v>3.12</v>
+      </c>
+      <c r="AB300">
+        <v>2.19</v>
+      </c>
+      <c r="AC300">
+        <v>1.03</v>
+      </c>
+      <c r="AD300">
+        <v>13</v>
+      </c>
+      <c r="AE300">
+        <v>1.25</v>
+      </c>
+      <c r="AF300">
+        <v>3.75</v>
+      </c>
+      <c r="AG300">
+        <v>1.8</v>
+      </c>
+      <c r="AH300">
+        <v>2</v>
+      </c>
+      <c r="AI300">
+        <v>1.62</v>
+      </c>
+      <c r="AJ300">
+        <v>2.2</v>
+      </c>
+      <c r="AK300">
+        <v>1.72</v>
+      </c>
+      <c r="AL300">
+        <v>1.25</v>
+      </c>
+      <c r="AM300">
+        <v>1.36</v>
+      </c>
+      <c r="AN300">
+        <v>1.27</v>
+      </c>
+      <c r="AO300">
+        <v>1.54</v>
+      </c>
+      <c r="AP300">
+        <v>1.17</v>
+      </c>
+      <c r="AQ300">
+        <v>1.64</v>
+      </c>
+      <c r="AR300">
+        <v>1.29</v>
+      </c>
+      <c r="AS300">
+        <v>1.29</v>
+      </c>
+      <c r="AT300">
+        <v>2.58</v>
+      </c>
+      <c r="AU300">
+        <v>3</v>
+      </c>
+      <c r="AV300">
+        <v>6</v>
+      </c>
+      <c r="AW300">
+        <v>3</v>
+      </c>
+      <c r="AX300">
+        <v>4</v>
+      </c>
+      <c r="AY300">
+        <v>6</v>
+      </c>
+      <c r="AZ300">
+        <v>10</v>
+      </c>
+      <c r="BA300">
+        <v>2</v>
+      </c>
+      <c r="BB300">
+        <v>6</v>
+      </c>
+      <c r="BC300">
+        <v>8</v>
+      </c>
+      <c r="BD300">
+        <v>2.23</v>
+      </c>
+      <c r="BE300">
+        <v>6.5</v>
+      </c>
+      <c r="BF300">
+        <v>1.8</v>
+      </c>
+      <c r="BG300">
+        <v>1.28</v>
+      </c>
+      <c r="BH300">
+        <v>3.2</v>
+      </c>
+      <c r="BI300">
+        <v>1.49</v>
+      </c>
+      <c r="BJ300">
+        <v>2.4</v>
+      </c>
+      <c r="BK300">
+        <v>1.8</v>
+      </c>
+      <c r="BL300">
+        <v>1.9</v>
+      </c>
+      <c r="BM300">
+        <v>2.23</v>
+      </c>
+      <c r="BN300">
+        <v>1.56</v>
+      </c>
+      <c r="BO300">
+        <v>2.9</v>
+      </c>
+      <c r="BP300">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="301" spans="1:68">
+      <c r="A301" s="1">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>7476862</v>
+      </c>
+      <c r="C301" t="s">
+        <v>68</v>
+      </c>
+      <c r="D301" t="s">
+        <v>69</v>
+      </c>
+      <c r="E301" s="2">
+        <v>45675.5</v>
+      </c>
+      <c r="F301">
+        <v>27</v>
+      </c>
+      <c r="G301" t="s">
+        <v>88</v>
+      </c>
+      <c r="H301" t="s">
+        <v>86</v>
+      </c>
+      <c r="I301">
+        <v>0</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>0</v>
+      </c>
+      <c r="L301">
+        <v>0</v>
+      </c>
+      <c r="M301">
+        <v>1</v>
+      </c>
+      <c r="N301">
+        <v>1</v>
+      </c>
+      <c r="O301" t="s">
+        <v>101</v>
+      </c>
+      <c r="P301" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q301">
+        <v>4</v>
+      </c>
+      <c r="R301">
+        <v>2.05</v>
+      </c>
+      <c r="S301">
+        <v>2.88</v>
+      </c>
+      <c r="T301">
+        <v>1.44</v>
+      </c>
+      <c r="U301">
+        <v>2.63</v>
+      </c>
+      <c r="V301">
+        <v>3.25</v>
+      </c>
+      <c r="W301">
+        <v>1.33</v>
+      </c>
+      <c r="X301">
+        <v>10</v>
+      </c>
+      <c r="Y301">
+        <v>1.06</v>
+      </c>
+      <c r="Z301">
+        <v>3.13</v>
+      </c>
+      <c r="AA301">
+        <v>3.03</v>
+      </c>
+      <c r="AB301">
+        <v>2.03</v>
+      </c>
+      <c r="AC301">
+        <v>1.07</v>
+      </c>
+      <c r="AD301">
+        <v>8</v>
+      </c>
+      <c r="AE301">
+        <v>1.38</v>
+      </c>
+      <c r="AF301">
+        <v>3</v>
+      </c>
+      <c r="AG301">
+        <v>2.06</v>
+      </c>
+      <c r="AH301">
+        <v>1.68</v>
+      </c>
+      <c r="AI301">
+        <v>1.83</v>
+      </c>
+      <c r="AJ301">
+        <v>1.83</v>
+      </c>
+      <c r="AK301">
+        <v>1.67</v>
+      </c>
+      <c r="AL301">
+        <v>1.28</v>
+      </c>
+      <c r="AM301">
+        <v>1.3</v>
+      </c>
+      <c r="AN301">
+        <v>0.55</v>
+      </c>
+      <c r="AO301">
+        <v>1.38</v>
+      </c>
+      <c r="AP301">
+        <v>0.5</v>
+      </c>
+      <c r="AQ301">
+        <v>1.5</v>
+      </c>
+      <c r="AR301">
+        <v>1.31</v>
+      </c>
+      <c r="AS301">
+        <v>1.12</v>
+      </c>
+      <c r="AT301">
+        <v>2.43</v>
+      </c>
+      <c r="AU301">
+        <v>4</v>
+      </c>
+      <c r="AV301">
+        <v>3</v>
+      </c>
+      <c r="AW301">
+        <v>12</v>
+      </c>
+      <c r="AX301">
+        <v>6</v>
+      </c>
+      <c r="AY301">
+        <v>19</v>
+      </c>
+      <c r="AZ301">
+        <v>10</v>
+      </c>
+      <c r="BA301">
+        <v>7</v>
+      </c>
+      <c r="BB301">
+        <v>4</v>
+      </c>
+      <c r="BC301">
+        <v>11</v>
+      </c>
+      <c r="BD301">
+        <v>2.43</v>
+      </c>
+      <c r="BE301">
+        <v>6.75</v>
+      </c>
+      <c r="BF301">
+        <v>1.66</v>
+      </c>
+      <c r="BG301">
+        <v>1.16</v>
+      </c>
+      <c r="BH301">
+        <v>4.6</v>
+      </c>
+      <c r="BI301">
+        <v>1.28</v>
+      </c>
+      <c r="BJ301">
+        <v>3.2</v>
+      </c>
+      <c r="BK301">
+        <v>1.48</v>
+      </c>
+      <c r="BL301">
+        <v>2.45</v>
+      </c>
+      <c r="BM301">
+        <v>1.74</v>
+      </c>
+      <c r="BN301">
+        <v>1.96</v>
+      </c>
+      <c r="BO301">
+        <v>2.12</v>
+      </c>
+      <c r="BP301">
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="401">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -847,6 +847,9 @@
     <t>['48', '81']</t>
   </si>
   <si>
+    <t>['33', '68']</t>
+  </si>
+  <si>
     <t>['1', '9']</t>
   </si>
   <si>
@@ -1575,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP301"/>
+  <dimension ref="A1:BP303"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2037,7 +2040,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2449,7 +2452,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -2939,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ7">
         <v>1.46</v>
@@ -3067,7 +3070,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -3273,7 +3276,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3351,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ9">
         <v>1.58</v>
@@ -3479,7 +3482,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3685,7 +3688,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4715,7 +4718,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5002,7 +5005,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5127,7 +5130,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5333,7 +5336,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -6157,7 +6160,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6569,7 +6572,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6775,7 +6778,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7599,7 +7602,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -8089,7 +8092,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -9041,7 +9044,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9247,7 +9250,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9659,7 +9662,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10071,7 +10074,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10149,7 +10152,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ42">
         <v>0.6899999999999999</v>
@@ -10483,7 +10486,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10689,7 +10692,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -11307,7 +11310,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11594,7 +11597,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ49">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR49">
         <v>1.1</v>
@@ -11719,7 +11722,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11925,7 +11928,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -13857,7 +13860,7 @@
         <v>1.5</v>
       </c>
       <c r="AP60">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ60">
         <v>1.62</v>
@@ -14066,7 +14069,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ61">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR61">
         <v>1.47</v>
@@ -14603,7 +14606,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -15015,7 +15018,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15633,7 +15636,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15839,7 +15842,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16045,7 +16048,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16251,7 +16254,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16663,7 +16666,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16869,7 +16872,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17075,7 +17078,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17487,7 +17490,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -18517,7 +18520,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -18595,7 +18598,7 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ83">
         <v>1.08</v>
@@ -19213,7 +19216,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ86">
         <v>1.08</v>
@@ -19753,7 +19756,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -20040,7 +20043,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ90">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR90">
         <v>1.27</v>
@@ -20165,7 +20168,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20371,7 +20374,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20577,7 +20580,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -20989,7 +20992,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21195,7 +21198,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -21273,10 +21276,10 @@
         <v>0.25</v>
       </c>
       <c r="AP96">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ96">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR96">
         <v>1.14</v>
@@ -21813,7 +21816,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q99">
         <v>4.5</v>
@@ -22019,7 +22022,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22431,7 +22434,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22637,7 +22640,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22843,7 +22846,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23255,7 +23258,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -23539,7 +23542,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ107">
         <v>1.58</v>
@@ -24697,7 +24700,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24903,7 +24906,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25521,7 +25524,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q117">
         <v>2.05</v>
@@ -25727,7 +25730,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25933,7 +25936,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26139,7 +26142,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26629,7 +26632,7 @@
         <v>0.6</v>
       </c>
       <c r="AP122">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ122">
         <v>0.64</v>
@@ -26757,7 +26760,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -27169,7 +27172,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27581,7 +27584,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27787,7 +27790,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -28405,7 +28408,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28611,7 +28614,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28817,7 +28820,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -29023,7 +29026,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q134">
         <v>4</v>
@@ -29104,7 +29107,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ134">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR134">
         <v>1.35</v>
@@ -29229,7 +29232,7 @@
         <v>147</v>
       </c>
       <c r="P135" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q135">
         <v>2.6</v>
@@ -29435,7 +29438,7 @@
         <v>186</v>
       </c>
       <c r="P136" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q136">
         <v>3.6</v>
@@ -29641,7 +29644,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q137">
         <v>3</v>
@@ -29847,7 +29850,7 @@
         <v>185</v>
       </c>
       <c r="P138" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q138">
         <v>2.5</v>
@@ -30259,7 +30262,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -30465,7 +30468,7 @@
         <v>101</v>
       </c>
       <c r="P141" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q141">
         <v>3</v>
@@ -31161,7 +31164,7 @@
         <v>2.17</v>
       </c>
       <c r="AP144">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ144">
         <v>1.71</v>
@@ -31289,7 +31292,7 @@
         <v>101</v>
       </c>
       <c r="P145" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31573,7 +31576,7 @@
         <v>1.4</v>
       </c>
       <c r="AP146">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ146">
         <v>1.5</v>
@@ -31907,7 +31910,7 @@
         <v>192</v>
       </c>
       <c r="P148" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -32731,7 +32734,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32937,7 +32940,7 @@
         <v>195</v>
       </c>
       <c r="P153" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33349,7 +33352,7 @@
         <v>196</v>
       </c>
       <c r="P155" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q155">
         <v>3</v>
@@ -33761,7 +33764,7 @@
         <v>198</v>
       </c>
       <c r="P157" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q157">
         <v>3.4</v>
@@ -33842,7 +33845,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ157">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR157">
         <v>1.15</v>
@@ -34585,7 +34588,7 @@
         <v>202</v>
       </c>
       <c r="P161" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q161">
         <v>3.2</v>
@@ -35203,7 +35206,7 @@
         <v>203</v>
       </c>
       <c r="P164" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q164">
         <v>2.4</v>
@@ -35281,7 +35284,7 @@
         <v>1.17</v>
       </c>
       <c r="AP164">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ164">
         <v>1.5</v>
@@ -35409,7 +35412,7 @@
         <v>101</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q165">
         <v>2.63</v>
@@ -35615,7 +35618,7 @@
         <v>204</v>
       </c>
       <c r="P166" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35693,7 +35696,7 @@
         <v>0.57</v>
       </c>
       <c r="AP166">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ166">
         <v>1.08</v>
@@ -35821,7 +35824,7 @@
         <v>205</v>
       </c>
       <c r="P167" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -36233,7 +36236,7 @@
         <v>207</v>
       </c>
       <c r="P169" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q169">
         <v>2.5</v>
@@ -36723,7 +36726,7 @@
         <v>1.14</v>
       </c>
       <c r="AP171">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ171">
         <v>1.08</v>
@@ -37057,7 +37060,7 @@
         <v>101</v>
       </c>
       <c r="P173" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q173">
         <v>2.1</v>
@@ -37263,7 +37266,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -38293,7 +38296,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q179">
         <v>2.3</v>
@@ -38577,7 +38580,7 @@
         <v>1.86</v>
       </c>
       <c r="AP180">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ180">
         <v>1.31</v>
@@ -39117,7 +39120,7 @@
         <v>214</v>
       </c>
       <c r="P183" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q183">
         <v>3.2</v>
@@ -39529,7 +39532,7 @@
         <v>185</v>
       </c>
       <c r="P185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q185">
         <v>3.4</v>
@@ -39941,7 +39944,7 @@
         <v>217</v>
       </c>
       <c r="P187" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q187">
         <v>2.2</v>
@@ -40559,7 +40562,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -40765,7 +40768,7 @@
         <v>148</v>
       </c>
       <c r="P191" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q191">
         <v>2.3</v>
@@ -40971,7 +40974,7 @@
         <v>219</v>
       </c>
       <c r="P192" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -42001,7 +42004,7 @@
         <v>221</v>
       </c>
       <c r="P197" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42207,7 +42210,7 @@
         <v>101</v>
       </c>
       <c r="P198" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q198">
         <v>3.75</v>
@@ -42413,7 +42416,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -42697,7 +42700,7 @@
         <v>1</v>
       </c>
       <c r="AP200">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ200">
         <v>1.08</v>
@@ -43031,7 +43034,7 @@
         <v>223</v>
       </c>
       <c r="P202" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q202">
         <v>1.8</v>
@@ -43237,7 +43240,7 @@
         <v>208</v>
       </c>
       <c r="P203" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43443,7 +43446,7 @@
         <v>224</v>
       </c>
       <c r="P204" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q204">
         <v>3.55</v>
@@ -43855,7 +43858,7 @@
         <v>226</v>
       </c>
       <c r="P206" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q206">
         <v>2.85</v>
@@ -44267,7 +44270,7 @@
         <v>228</v>
       </c>
       <c r="P208" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q208">
         <v>2.4</v>
@@ -44473,7 +44476,7 @@
         <v>229</v>
       </c>
       <c r="P209" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44885,7 +44888,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q211">
         <v>3.5</v>
@@ -44963,7 +44966,7 @@
         <v>1.75</v>
       </c>
       <c r="AP211">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ211">
         <v>1.62</v>
@@ -45709,7 +45712,7 @@
         <v>234</v>
       </c>
       <c r="P215" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -46121,7 +46124,7 @@
         <v>236</v>
       </c>
       <c r="P217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46327,7 +46330,7 @@
         <v>101</v>
       </c>
       <c r="P218" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46405,7 +46408,7 @@
         <v>1.25</v>
       </c>
       <c r="AP218">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ218">
         <v>1.45</v>
@@ -46739,7 +46742,7 @@
         <v>101</v>
       </c>
       <c r="P220" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47151,7 +47154,7 @@
         <v>239</v>
       </c>
       <c r="P222" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q222">
         <v>2.38</v>
@@ -48181,7 +48184,7 @@
         <v>101</v>
       </c>
       <c r="P227" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48799,7 +48802,7 @@
         <v>101</v>
       </c>
       <c r="P230" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -49005,7 +49008,7 @@
         <v>101</v>
       </c>
       <c r="P231" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q231">
         <v>3.4</v>
@@ -49211,7 +49214,7 @@
         <v>240</v>
       </c>
       <c r="P232" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -49289,7 +49292,7 @@
         <v>0.78</v>
       </c>
       <c r="AP232">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ232">
         <v>0.92</v>
@@ -49417,7 +49420,7 @@
         <v>241</v>
       </c>
       <c r="P233" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q233">
         <v>2.88</v>
@@ -50241,7 +50244,7 @@
         <v>244</v>
       </c>
       <c r="P237" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q237">
         <v>4.5</v>
@@ -50322,7 +50325,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ237">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR237">
         <v>1.15</v>
@@ -50447,7 +50450,7 @@
         <v>101</v>
       </c>
       <c r="P238" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q238">
         <v>5.5</v>
@@ -50525,7 +50528,7 @@
         <v>1.89</v>
       </c>
       <c r="AP238">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ238">
         <v>2.09</v>
@@ -50859,7 +50862,7 @@
         <v>246</v>
       </c>
       <c r="P240" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q240">
         <v>2.88</v>
@@ -51271,7 +51274,7 @@
         <v>101</v>
       </c>
       <c r="P242" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q242">
         <v>3.75</v>
@@ -51477,7 +51480,7 @@
         <v>101</v>
       </c>
       <c r="P243" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q243">
         <v>3.5</v>
@@ -52301,7 +52304,7 @@
         <v>101</v>
       </c>
       <c r="P247" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q247">
         <v>2.6</v>
@@ -52507,7 +52510,7 @@
         <v>249</v>
       </c>
       <c r="P248" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q248">
         <v>2.38</v>
@@ -52791,7 +52794,7 @@
         <v>1.6</v>
       </c>
       <c r="AP249">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ249">
         <v>1.31</v>
@@ -53125,7 +53128,7 @@
         <v>101</v>
       </c>
       <c r="P251" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q251">
         <v>2.5</v>
@@ -53743,7 +53746,7 @@
         <v>254</v>
       </c>
       <c r="P254" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q254">
         <v>2.25</v>
@@ -53949,7 +53952,7 @@
         <v>255</v>
       </c>
       <c r="P255" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q255">
         <v>2.1</v>
@@ -54155,7 +54158,7 @@
         <v>114</v>
       </c>
       <c r="P256" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q256">
         <v>2.88</v>
@@ -55391,7 +55394,7 @@
         <v>259</v>
       </c>
       <c r="P262" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q262">
         <v>3.6</v>
@@ -55675,7 +55678,7 @@
         <v>0.82</v>
       </c>
       <c r="AP263">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ263">
         <v>1</v>
@@ -56627,7 +56630,7 @@
         <v>101</v>
       </c>
       <c r="P268" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -56705,7 +56708,7 @@
         <v>1.2</v>
       </c>
       <c r="AP268">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ268">
         <v>1.5</v>
@@ -56833,7 +56836,7 @@
         <v>261</v>
       </c>
       <c r="P269" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q269">
         <v>2.4</v>
@@ -57039,7 +57042,7 @@
         <v>184</v>
       </c>
       <c r="P270" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q270">
         <v>3.25</v>
@@ -57451,7 +57454,7 @@
         <v>263</v>
       </c>
       <c r="P272" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q272">
         <v>3.1</v>
@@ -57657,7 +57660,7 @@
         <v>264</v>
       </c>
       <c r="P273" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q273">
         <v>2.75</v>
@@ -58069,7 +58072,7 @@
         <v>265</v>
       </c>
       <c r="P275" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q275">
         <v>2.88</v>
@@ -58150,7 +58153,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ275">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR275">
         <v>1.46</v>
@@ -58275,7 +58278,7 @@
         <v>266</v>
       </c>
       <c r="P276" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q276">
         <v>3.1</v>
@@ -58481,7 +58484,7 @@
         <v>267</v>
       </c>
       <c r="P277" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q277">
         <v>3.4</v>
@@ -58687,7 +58690,7 @@
         <v>101</v>
       </c>
       <c r="P278" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q278">
         <v>3.1</v>
@@ -58893,7 +58896,7 @@
         <v>128</v>
       </c>
       <c r="P279" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q279">
         <v>5</v>
@@ -60129,7 +60132,7 @@
         <v>101</v>
       </c>
       <c r="P285" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60335,7 +60338,7 @@
         <v>101</v>
       </c>
       <c r="P286" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q286">
         <v>2.6</v>
@@ -60541,7 +60544,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -61237,7 +61240,7 @@
         <v>0.91</v>
       </c>
       <c r="AP290">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ290">
         <v>0.83</v>
@@ -61365,7 +61368,7 @@
         <v>101</v>
       </c>
       <c r="P291" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q291">
         <v>4</v>
@@ -61777,7 +61780,7 @@
         <v>273</v>
       </c>
       <c r="P293" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q293">
         <v>2</v>
@@ -61983,7 +61986,7 @@
         <v>101</v>
       </c>
       <c r="P294" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q294">
         <v>2.88</v>
@@ -62395,7 +62398,7 @@
         <v>101</v>
       </c>
       <c r="P296" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q296">
         <v>2.75</v>
@@ -62601,7 +62604,7 @@
         <v>274</v>
       </c>
       <c r="P297" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q297">
         <v>2.38</v>
@@ -62682,7 +62685,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ297">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR297">
         <v>1.58</v>
@@ -63219,7 +63222,7 @@
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63425,7 +63428,7 @@
         <v>101</v>
       </c>
       <c r="P301" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q301">
         <v>4</v>
@@ -63582,6 +63585,418 @@
       </c>
       <c r="BP301">
         <v>1.64</v>
+      </c>
+    </row>
+    <row r="302" spans="1:68">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>7476849</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" t="s">
+        <v>69</v>
+      </c>
+      <c r="E302" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F302">
+        <v>26</v>
+      </c>
+      <c r="G302" t="s">
+        <v>77</v>
+      </c>
+      <c r="H302" t="s">
+        <v>85</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>0</v>
+      </c>
+      <c r="M302">
+        <v>0</v>
+      </c>
+      <c r="N302">
+        <v>0</v>
+      </c>
+      <c r="O302" t="s">
+        <v>101</v>
+      </c>
+      <c r="P302" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q302">
+        <v>4.5</v>
+      </c>
+      <c r="R302">
+        <v>2.05</v>
+      </c>
+      <c r="S302">
+        <v>2.63</v>
+      </c>
+      <c r="T302">
+        <v>1.44</v>
+      </c>
+      <c r="U302">
+        <v>2.63</v>
+      </c>
+      <c r="V302">
+        <v>3.25</v>
+      </c>
+      <c r="W302">
+        <v>1.33</v>
+      </c>
+      <c r="X302">
+        <v>10</v>
+      </c>
+      <c r="Y302">
+        <v>1.06</v>
+      </c>
+      <c r="Z302">
+        <v>3.7</v>
+      </c>
+      <c r="AA302">
+        <v>3.4</v>
+      </c>
+      <c r="AB302">
+        <v>2.05</v>
+      </c>
+      <c r="AC302">
+        <v>1.06</v>
+      </c>
+      <c r="AD302">
+        <v>9.5</v>
+      </c>
+      <c r="AE302">
+        <v>1.38</v>
+      </c>
+      <c r="AF302">
+        <v>3</v>
+      </c>
+      <c r="AG302">
+        <v>2.1</v>
+      </c>
+      <c r="AH302">
+        <v>1.67</v>
+      </c>
+      <c r="AI302">
+        <v>1.91</v>
+      </c>
+      <c r="AJ302">
+        <v>1.8</v>
+      </c>
+      <c r="AK302">
+        <v>1.75</v>
+      </c>
+      <c r="AL302">
+        <v>1.31</v>
+      </c>
+      <c r="AM302">
+        <v>1.27</v>
+      </c>
+      <c r="AN302">
+        <v>1.15</v>
+      </c>
+      <c r="AO302">
+        <v>1.08</v>
+      </c>
+      <c r="AP302">
+        <v>1.14</v>
+      </c>
+      <c r="AQ302">
+        <v>1.08</v>
+      </c>
+      <c r="AR302">
+        <v>1.08</v>
+      </c>
+      <c r="AS302">
+        <v>1.07</v>
+      </c>
+      <c r="AT302">
+        <v>2.15</v>
+      </c>
+      <c r="AU302">
+        <v>2</v>
+      </c>
+      <c r="AV302">
+        <v>5</v>
+      </c>
+      <c r="AW302">
+        <v>7</v>
+      </c>
+      <c r="AX302">
+        <v>11</v>
+      </c>
+      <c r="AY302">
+        <v>10</v>
+      </c>
+      <c r="AZ302">
+        <v>22</v>
+      </c>
+      <c r="BA302">
+        <v>1</v>
+      </c>
+      <c r="BB302">
+        <v>8</v>
+      </c>
+      <c r="BC302">
+        <v>9</v>
+      </c>
+      <c r="BD302">
+        <v>2.85</v>
+      </c>
+      <c r="BE302">
+        <v>6.75</v>
+      </c>
+      <c r="BF302">
+        <v>1.65</v>
+      </c>
+      <c r="BG302">
+        <v>1.18</v>
+      </c>
+      <c r="BH302">
+        <v>3.9</v>
+      </c>
+      <c r="BI302">
+        <v>1.37</v>
+      </c>
+      <c r="BJ302">
+        <v>2.75</v>
+      </c>
+      <c r="BK302">
+        <v>1.7</v>
+      </c>
+      <c r="BL302">
+        <v>2.05</v>
+      </c>
+      <c r="BM302">
+        <v>2.09</v>
+      </c>
+      <c r="BN302">
+        <v>1.63</v>
+      </c>
+      <c r="BO302">
+        <v>2.7</v>
+      </c>
+      <c r="BP302">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="303" spans="1:68">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>7476741</v>
+      </c>
+      <c r="C303" t="s">
+        <v>68</v>
+      </c>
+      <c r="D303" t="s">
+        <v>69</v>
+      </c>
+      <c r="E303" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F303">
+        <v>17</v>
+      </c>
+      <c r="G303" t="s">
+        <v>75</v>
+      </c>
+      <c r="H303" t="s">
+        <v>78</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>1</v>
+      </c>
+      <c r="L303">
+        <v>2</v>
+      </c>
+      <c r="M303">
+        <v>1</v>
+      </c>
+      <c r="N303">
+        <v>3</v>
+      </c>
+      <c r="O303" t="s">
+        <v>277</v>
+      </c>
+      <c r="P303" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q303">
+        <v>2.88</v>
+      </c>
+      <c r="R303">
+        <v>2.25</v>
+      </c>
+      <c r="S303">
+        <v>3.4</v>
+      </c>
+      <c r="T303">
+        <v>1.33</v>
+      </c>
+      <c r="U303">
+        <v>3.25</v>
+      </c>
+      <c r="V303">
+        <v>2.63</v>
+      </c>
+      <c r="W303">
+        <v>1.44</v>
+      </c>
+      <c r="X303">
+        <v>7</v>
+      </c>
+      <c r="Y303">
+        <v>1.1</v>
+      </c>
+      <c r="Z303">
+        <v>2.3</v>
+      </c>
+      <c r="AA303">
+        <v>3.6</v>
+      </c>
+      <c r="AB303">
+        <v>2.9</v>
+      </c>
+      <c r="AC303">
+        <v>1.05</v>
+      </c>
+      <c r="AD303">
+        <v>9</v>
+      </c>
+      <c r="AE303">
+        <v>1.28</v>
+      </c>
+      <c r="AF303">
+        <v>3.55</v>
+      </c>
+      <c r="AG303">
+        <v>1.75</v>
+      </c>
+      <c r="AH303">
+        <v>1.95</v>
+      </c>
+      <c r="AI303">
+        <v>1.62</v>
+      </c>
+      <c r="AJ303">
+        <v>2.2</v>
+      </c>
+      <c r="AK303">
+        <v>1.45</v>
+      </c>
+      <c r="AL303">
+        <v>1.25</v>
+      </c>
+      <c r="AM303">
+        <v>1.48</v>
+      </c>
+      <c r="AN303">
+        <v>1.33</v>
+      </c>
+      <c r="AO303">
+        <v>1.3</v>
+      </c>
+      <c r="AP303">
+        <v>1.46</v>
+      </c>
+      <c r="AQ303">
+        <v>1.18</v>
+      </c>
+      <c r="AR303">
+        <v>1.31</v>
+      </c>
+      <c r="AS303">
+        <v>1.42</v>
+      </c>
+      <c r="AT303">
+        <v>2.73</v>
+      </c>
+      <c r="AU303">
+        <v>7</v>
+      </c>
+      <c r="AV303">
+        <v>4</v>
+      </c>
+      <c r="AW303">
+        <v>7</v>
+      </c>
+      <c r="AX303">
+        <v>3</v>
+      </c>
+      <c r="AY303">
+        <v>14</v>
+      </c>
+      <c r="AZ303">
+        <v>7</v>
+      </c>
+      <c r="BA303">
+        <v>3</v>
+      </c>
+      <c r="BB303">
+        <v>1</v>
+      </c>
+      <c r="BC303">
+        <v>4</v>
+      </c>
+      <c r="BD303">
+        <v>1.82</v>
+      </c>
+      <c r="BE303">
+        <v>7</v>
+      </c>
+      <c r="BF303">
+        <v>2.43</v>
+      </c>
+      <c r="BG303">
+        <v>1.27</v>
+      </c>
+      <c r="BH303">
+        <v>3.38</v>
+      </c>
+      <c r="BI303">
+        <v>1.49</v>
+      </c>
+      <c r="BJ303">
+        <v>2.44</v>
+      </c>
+      <c r="BK303">
+        <v>1.82</v>
+      </c>
+      <c r="BL303">
+        <v>1.98</v>
+      </c>
+      <c r="BM303">
+        <v>2.32</v>
+      </c>
+      <c r="BN303">
+        <v>1.54</v>
+      </c>
+      <c r="BO303">
+        <v>3.05</v>
+      </c>
+      <c r="BP303">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League Two_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="402">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -835,19 +835,22 @@
     <t>['34', '56']</t>
   </si>
   <si>
-    <t>['29', '62', '77']</t>
-  </si>
-  <si>
-    <t>['32', '46', '66', '81']</t>
-  </si>
-  <si>
     <t>['8', '87']</t>
   </si>
   <si>
     <t>['48', '81']</t>
   </si>
   <si>
+    <t>['32', '46', '66', '81']</t>
+  </si>
+  <si>
+    <t>['29', '62', '77']</t>
+  </si>
+  <si>
     <t>['33', '68']</t>
+  </si>
+  <si>
+    <t>['12']</t>
   </si>
   <si>
     <t>['1', '9']</t>
@@ -1007,9 +1010,6 @@
   </si>
   <si>
     <t>['58', '90+4']</t>
-  </si>
-  <si>
-    <t>['12']</t>
   </si>
   <si>
     <t>['2', '22', '49']</t>
@@ -1195,28 +1195,31 @@
     <t>['49', '77']</t>
   </si>
   <si>
-    <t>['56', '61']</t>
+    <t>['18', '59']</t>
   </si>
   <si>
-    <t>['18', '59']</t>
+    <t>['56', '61']</t>
   </si>
   <si>
     <t>['33']</t>
   </si>
   <si>
-    <t>['12', '33']</t>
+    <t>['4']</t>
   </si>
   <si>
-    <t>['4']</t>
+    <t>['16', '27', '63']</t>
+  </si>
+  <si>
+    <t>['14', '85']</t>
   </si>
   <si>
     <t>['2', '11']</t>
   </si>
   <si>
-    <t>['14', '85']</t>
+    <t>['12', '33']</t>
   </si>
   <si>
-    <t>['16', '27', '63']</t>
+    <t>['15', '75']</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP303"/>
+  <dimension ref="A1:BP304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1915,7 +1918,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2040,7 +2043,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -2452,7 +2455,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q5">
         <v>2.4</v>
@@ -3070,7 +3073,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -3276,7 +3279,7 @@
         <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q9">
         <v>2.75</v>
@@ -3482,7 +3485,7 @@
         <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q10">
         <v>2.63</v>
@@ -3688,7 +3691,7 @@
         <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4718,7 +4721,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5130,7 +5133,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5336,7 +5339,7 @@
         <v>107</v>
       </c>
       <c r="P19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -5826,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ21">
         <v>1.62</v>
@@ -6160,7 +6163,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6572,7 +6575,7 @@
         <v>109</v>
       </c>
       <c r="P25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6778,7 +6781,7 @@
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7271,7 +7274,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ28">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR28">
         <v>1.35</v>
@@ -7602,7 +7605,7 @@
         <v>112</v>
       </c>
       <c r="P30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7680,7 +7683,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ30">
         <v>0.92</v>
@@ -9044,7 +9047,7 @@
         <v>101</v>
       </c>
       <c r="P37" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q37">
         <v>2.6</v>
@@ -9250,7 +9253,7 @@
         <v>117</v>
       </c>
       <c r="P38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9662,7 +9665,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10074,7 +10077,7 @@
         <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q42">
         <v>3.75</v>
@@ -10486,7 +10489,7 @@
         <v>121</v>
       </c>
       <c r="P44" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q44">
         <v>2.75</v>
@@ -10692,7 +10695,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -11310,7 +11313,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -11722,7 +11725,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11800,7 +11803,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ50">
         <v>1.71</v>
@@ -11928,7 +11931,7 @@
         <v>103</v>
       </c>
       <c r="P51" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q51">
         <v>2.5</v>
@@ -12009,7 +12012,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ51">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR51">
         <v>1.28</v>
@@ -14606,7 +14609,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q64">
         <v>3</v>
@@ -15018,7 +15021,7 @@
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q66">
         <v>3.75</v>
@@ -15636,7 +15639,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -15842,7 +15845,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q70">
         <v>3.25</v>
@@ -16048,7 +16051,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q71">
         <v>3</v>
@@ -16254,7 +16257,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q72">
         <v>4</v>
@@ -16666,7 +16669,7 @@
         <v>101</v>
       </c>
       <c r="P74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q74">
         <v>2.63</v>
@@ -16872,7 +16875,7 @@
         <v>101</v>
       </c>
       <c r="P75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q75">
         <v>3.4</v>
@@ -17078,7 +17081,7 @@
         <v>101</v>
       </c>
       <c r="P76" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q76">
         <v>2.6</v>
@@ -17490,7 +17493,7 @@
         <v>149</v>
       </c>
       <c r="P78" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -18520,7 +18523,7 @@
         <v>153</v>
       </c>
       <c r="P83" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q83">
         <v>2.2</v>
@@ -19631,7 +19634,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ88">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR88">
         <v>1.3</v>
@@ -19756,7 +19759,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -19834,7 +19837,7 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ89">
         <v>1.5</v>
@@ -20168,7 +20171,7 @@
         <v>101</v>
       </c>
       <c r="P91" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -20374,7 +20377,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -20580,7 +20583,7 @@
         <v>159</v>
       </c>
       <c r="P93" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q93">
         <v>2.75</v>
@@ -20992,7 +20995,7 @@
         <v>161</v>
       </c>
       <c r="P95" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q95">
         <v>2.5</v>
@@ -21198,7 +21201,7 @@
         <v>162</v>
       </c>
       <c r="P96" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q96">
         <v>4.5</v>
@@ -21485,7 +21488,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ97">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR97">
         <v>1.07</v>
@@ -21688,7 +21691,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ98">
         <v>1.5</v>
@@ -21816,7 +21819,7 @@
         <v>165</v>
       </c>
       <c r="P99" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q99">
         <v>4.5</v>
@@ -22022,7 +22025,7 @@
         <v>166</v>
       </c>
       <c r="P100" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q100">
         <v>2.75</v>
@@ -22434,7 +22437,7 @@
         <v>167</v>
       </c>
       <c r="P102" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22640,7 +22643,7 @@
         <v>101</v>
       </c>
       <c r="P103" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -22846,7 +22849,7 @@
         <v>168</v>
       </c>
       <c r="P104" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -23258,7 +23261,7 @@
         <v>101</v>
       </c>
       <c r="P106" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q106">
         <v>3.6</v>
@@ -24700,7 +24703,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q113">
         <v>2.6</v>
@@ -24906,7 +24909,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25524,7 +25527,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q117">
         <v>2.05</v>
@@ -25730,7 +25733,7 @@
         <v>176</v>
       </c>
       <c r="P118" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25936,7 +25939,7 @@
         <v>101</v>
       </c>
       <c r="P119" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q119">
         <v>3.4</v>
@@ -26142,7 +26145,7 @@
         <v>94</v>
       </c>
       <c r="P120" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q120">
         <v>2.88</v>
@@ -26760,7 +26763,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q123">
         <v>2.38</v>
@@ -27172,7 +27175,7 @@
         <v>101</v>
       </c>
       <c r="P125" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q125">
         <v>2.1</v>
@@ -27584,7 +27587,7 @@
         <v>180</v>
       </c>
       <c r="P127" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27665,7 +27668,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ127">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27790,7 +27793,7 @@
         <v>101</v>
       </c>
       <c r="P128" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q128">
         <v>4.75</v>
@@ -27868,7 +27871,7 @@
         <v>1.4</v>
       </c>
       <c r="AP128">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ128">
         <v>1.31</v>
@@ -28408,7 +28411,7 @@
         <v>182</v>
       </c>
       <c r="P131" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q131">
         <v>2.63</v>
@@ -28614,7 +28617,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28820,7 +28823,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -29850,7 +29853,7 @@
         <v>185</v>
       </c>
       <c r="P138" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q138">
         <v>2.5</v>
@@ -30262,7 +30265,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q140">
         <v>2.25</v>
@@ -30755,7 +30758,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ142">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR142">
         <v>1.41</v>
@@ -33224,7 +33227,7 @@
         <v>1.67</v>
       </c>
       <c r="AP154">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ154">
         <v>1.27</v>
@@ -35412,7 +35415,7 @@
         <v>101</v>
       </c>
       <c r="P165" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q165">
         <v>2.63</v>
@@ -36317,7 +36320,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ169">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR169">
         <v>1.18</v>
@@ -37266,7 +37269,7 @@
         <v>148</v>
       </c>
       <c r="P174" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q174">
         <v>3.2</v>
@@ -38168,7 +38171,7 @@
         <v>1.88</v>
       </c>
       <c r="AP178">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ178">
         <v>1.46</v>
@@ -39201,7 +39204,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ183">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR183">
         <v>1.27</v>
@@ -40562,7 +40565,7 @@
         <v>101</v>
       </c>
       <c r="P190" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q190">
         <v>3.25</v>
@@ -42416,7 +42419,7 @@
         <v>122</v>
       </c>
       <c r="P199" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q199">
         <v>3.4</v>
@@ -43733,7 +43736,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ205">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR205">
         <v>1.62</v>
@@ -47853,7 +47856,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ225">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR225">
         <v>1.48</v>
@@ -50322,7 +50325,7 @@
         <v>1.43</v>
       </c>
       <c r="AP237">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ237">
         <v>1.18</v>
@@ -52510,7 +52513,7 @@
         <v>249</v>
       </c>
       <c r="P248" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q248">
         <v>2.38</v>
@@ -53827,7 +53830,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ254">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR254">
         <v>1.49</v>
@@ -54239,7 +54242,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ256">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR256">
         <v>1.49</v>
@@ -58974,7 +58977,7 @@
         <v>1.3</v>
       </c>
       <c r="AP279">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ279">
         <v>1.45</v>
@@ -59183,7 +59186,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ280">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR280">
         <v>1.76</v>
@@ -60090,7 +60093,7 @@
         <v>284</v>
       </c>
       <c r="B285">
-        <v>7476832</v>
+        <v>7476835</v>
       </c>
       <c r="C285" t="s">
         <v>68</v>
@@ -60105,19 +60108,19 @@
         <v>25</v>
       </c>
       <c r="G285" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="H285" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I285">
         <v>0</v>
       </c>
       <c r="J285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L285">
         <v>0</v>
@@ -60135,160 +60138,160 @@
         <v>393</v>
       </c>
       <c r="Q285">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R285">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S285">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="T285">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U285">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V285">
+        <v>2.75</v>
+      </c>
+      <c r="W285">
+        <v>1.4</v>
+      </c>
+      <c r="X285">
+        <v>8</v>
+      </c>
+      <c r="Y285">
+        <v>1.08</v>
+      </c>
+      <c r="Z285">
+        <v>1.83</v>
+      </c>
+      <c r="AA285">
         <v>3.4</v>
       </c>
-      <c r="W285">
-        <v>1.3</v>
-      </c>
-      <c r="X285">
-        <v>10</v>
-      </c>
-      <c r="Y285">
-        <v>1.06</v>
-      </c>
-      <c r="Z285">
-        <v>1.62</v>
-      </c>
-      <c r="AA285">
-        <v>3.6</v>
-      </c>
       <c r="AB285">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="AC285">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD285">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AE285">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AF285">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AG285">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH285">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AI285">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ285">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AK285">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL285">
         <v>1.25</v>
       </c>
       <c r="AM285">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AN285">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AO285">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="AP285">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AQ285">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR285">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AS285">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AT285">
-        <v>2.44</v>
+        <v>2.93</v>
       </c>
       <c r="AU285">
+        <v>0</v>
+      </c>
+      <c r="AV285">
+        <v>5</v>
+      </c>
+      <c r="AW285">
+        <v>3</v>
+      </c>
+      <c r="AX285">
+        <v>6</v>
+      </c>
+      <c r="AY285">
+        <v>9</v>
+      </c>
+      <c r="AZ285">
+        <v>13</v>
+      </c>
+      <c r="BA285">
         <v>4</v>
       </c>
-      <c r="AV285">
-        <v>4</v>
-      </c>
-      <c r="AW285">
-        <v>3</v>
-      </c>
-      <c r="AX285">
-        <v>1</v>
-      </c>
-      <c r="AY285">
-        <v>15</v>
-      </c>
-      <c r="AZ285">
-        <v>7</v>
-      </c>
-      <c r="BA285">
-        <v>7</v>
-      </c>
       <c r="BB285">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BC285">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BD285">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="BE285">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF285">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BG285">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BH285">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI285">
+        <v>1.55</v>
+      </c>
+      <c r="BJ285">
+        <v>2.28</v>
+      </c>
+      <c r="BK285">
+        <v>1.9</v>
+      </c>
+      <c r="BL285">
+        <v>1.79</v>
+      </c>
+      <c r="BM285">
+        <v>2.4</v>
+      </c>
+      <c r="BN285">
         <v>1.5</v>
       </c>
-      <c r="BJ285">
-        <v>2.38</v>
-      </c>
-      <c r="BK285">
-        <v>1.82</v>
-      </c>
-      <c r="BL285">
-        <v>1.86</v>
-      </c>
-      <c r="BM285">
-        <v>2.28</v>
-      </c>
-      <c r="BN285">
-        <v>1.55</v>
-      </c>
       <c r="BO285">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="BP285">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="286" spans="1:68">
@@ -60296,7 +60299,7 @@
         <v>285</v>
       </c>
       <c r="B286">
-        <v>7476835</v>
+        <v>7476832</v>
       </c>
       <c r="C286" t="s">
         <v>68</v>
@@ -60311,19 +60314,19 @@
         <v>25</v>
       </c>
       <c r="G286" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H286" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I286">
         <v>0</v>
       </c>
       <c r="J286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L286">
         <v>0</v>
@@ -60341,160 +60344,160 @@
         <v>394</v>
       </c>
       <c r="Q286">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R286">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S286">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="T286">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U286">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V286">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="W286">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="X286">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y286">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z286">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AA286">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB286">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="AC286">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD286">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AE286">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AF286">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="AG286">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH286">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AI286">
+        <v>2</v>
+      </c>
+      <c r="AJ286">
         <v>1.73</v>
       </c>
-      <c r="AJ286">
-        <v>2</v>
-      </c>
       <c r="AK286">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL286">
         <v>1.25</v>
       </c>
       <c r="AM286">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AN286">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AO286">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AP286">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AQ286">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR286">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AS286">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AT286">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="AU286">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV286">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW286">
         <v>3</v>
       </c>
       <c r="AX286">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AY286">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ286">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA286">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BB286">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC286">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BD286">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="BE286">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF286">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BG286">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="BH286">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BI286">
+        <v>1.5</v>
+      </c>
+      <c r="BJ286">
+        <v>2.38</v>
+      </c>
+      <c r="BK286">
+        <v>1.82</v>
+      </c>
+      <c r="BL286">
+        <v>1.86</v>
+      </c>
+      <c r="BM286">
+        <v>2.28</v>
+      </c>
+      <c r="BN286">
         <v>1.55</v>
       </c>
-      <c r="BJ286">
-        <v>2.28</v>
-      </c>
-      <c r="BK286">
-        <v>1.9</v>
-      </c>
-      <c r="BL286">
-        <v>1.79</v>
-      </c>
-      <c r="BM286">
-        <v>2.4</v>
-      </c>
-      <c r="BN286">
-        <v>1.5</v>
-      </c>
       <c r="BO286">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BP286">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="287" spans="1:68">
@@ -60544,7 +60547,7 @@
         <v>270</v>
       </c>
       <c r="P287" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q287">
         <v>2.75</v>
@@ -61738,7 +61741,7 @@
         <v>292</v>
       </c>
       <c r="B293">
-        <v>7476863</v>
+        <v>7476862</v>
       </c>
       <c r="C293" t="s">
         <v>68</v>
@@ -61753,88 +61756,88 @@
         <v>27</v>
       </c>
       <c r="G293" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H293" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J293">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K293">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L293">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M293">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N293">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O293" t="s">
-        <v>273</v>
+        <v>101</v>
       </c>
       <c r="P293" t="s">
-        <v>396</v>
+        <v>292</v>
       </c>
       <c r="Q293">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R293">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S293">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="T293">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U293">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V293">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="W293">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="X293">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y293">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z293">
-        <v>1.39</v>
+        <v>3.13</v>
       </c>
       <c r="AA293">
-        <v>3.91</v>
+        <v>3.03</v>
       </c>
       <c r="AB293">
-        <v>5.9</v>
+        <v>2.03</v>
       </c>
       <c r="AC293">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AD293">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE293">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF293">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AG293">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AH293">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AI293">
         <v>1.83</v>
@@ -61843,100 +61846,100 @@
         <v>1.83</v>
       </c>
       <c r="AK293">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="AL293">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AM293">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AN293">
-        <v>1.55</v>
+        <v>0.55</v>
       </c>
       <c r="AO293">
-        <v>0.6899999999999999</v>
+        <v>1.38</v>
       </c>
       <c r="AP293">
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="AQ293">
-        <v>0.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR293">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AS293">
-        <v>0.83</v>
+        <v>1.12</v>
       </c>
       <c r="AT293">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="AU293">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AV293">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW293">
         <v>12</v>
       </c>
       <c r="AX293">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY293">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AZ293">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA293">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB293">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC293">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BD293">
-        <v>1.38</v>
+        <v>2.43</v>
       </c>
       <c r="BE293">
         <v>6.75</v>
       </c>
       <c r="BF293">
-        <v>3.45</v>
+        <v>1.66</v>
       </c>
       <c r="BG293">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="BH293">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI293">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="BJ293">
-        <v>2.07</v>
+        <v>3.2</v>
       </c>
       <c r="BK293">
-        <v>2.07</v>
+        <v>1.48</v>
       </c>
       <c r="BL293">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="BM293">
-        <v>2.65</v>
+        <v>1.74</v>
       </c>
       <c r="BN293">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
       <c r="BO293">
-        <v>3.4</v>
+        <v>2.12</v>
       </c>
       <c r="BP293">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="294" spans="1:68">
@@ -61944,7 +61947,7 @@
         <v>293</v>
       </c>
       <c r="B294">
-        <v>7476857</v>
+        <v>7476865</v>
       </c>
       <c r="C294" t="s">
         <v>68</v>
@@ -61959,190 +61962,190 @@
         <v>27</v>
       </c>
       <c r="G294" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="H294" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K294">
         <v>1</v>
       </c>
       <c r="L294">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O294" t="s">
+        <v>273</v>
+      </c>
+      <c r="P294" t="s">
         <v>101</v>
       </c>
-      <c r="P294" t="s">
-        <v>397</v>
-      </c>
       <c r="Q294">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R294">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S294">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T294">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="U294">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V294">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W294">
+        <v>1.33</v>
+      </c>
+      <c r="X294">
+        <v>9</v>
+      </c>
+      <c r="Y294">
+        <v>1.07</v>
+      </c>
+      <c r="Z294">
+        <v>2.46</v>
+      </c>
+      <c r="AA294">
+        <v>2.96</v>
+      </c>
+      <c r="AB294">
+        <v>2.51</v>
+      </c>
+      <c r="AC294">
+        <v>1.07</v>
+      </c>
+      <c r="AD294">
+        <v>8</v>
+      </c>
+      <c r="AE294">
         <v>1.36</v>
       </c>
-      <c r="X294">
-        <v>8</v>
-      </c>
-      <c r="Y294">
-        <v>1.08</v>
-      </c>
-      <c r="Z294">
-        <v>2.2</v>
-      </c>
-      <c r="AA294">
-        <v>3.25</v>
-      </c>
-      <c r="AB294">
-        <v>3.2</v>
-      </c>
-      <c r="AC294">
-        <v>1.06</v>
-      </c>
-      <c r="AD294">
-        <v>8.5</v>
-      </c>
-      <c r="AE294">
-        <v>1.33</v>
-      </c>
       <c r="AF294">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AG294">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AH294">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI294">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ294">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AK294">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AL294">
         <v>1.28</v>
       </c>
       <c r="AM294">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AN294">
         <v>1.25</v>
       </c>
       <c r="AO294">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="AP294">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AQ294">
-        <v>1.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR294">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AS294">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AT294">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AU294">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV294">
+        <v>3</v>
+      </c>
+      <c r="AW294">
+        <v>10</v>
+      </c>
+      <c r="AX294">
+        <v>5</v>
+      </c>
+      <c r="AY294">
+        <v>18</v>
+      </c>
+      <c r="AZ294">
+        <v>11</v>
+      </c>
+      <c r="BA294">
         <v>6</v>
-      </c>
-      <c r="AW294">
-        <v>14</v>
-      </c>
-      <c r="AX294">
-        <v>4</v>
-      </c>
-      <c r="AY294">
-        <v>20</v>
-      </c>
-      <c r="AZ294">
-        <v>12</v>
-      </c>
-      <c r="BA294">
-        <v>8</v>
       </c>
       <c r="BB294">
         <v>4</v>
       </c>
       <c r="BC294">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BD294">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BE294">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="BF294">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="BG294">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BH294">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="BI294">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="BJ294">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="BK294">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="BL294">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="BM294">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="BN294">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="BO294">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="BP294">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="295" spans="1:68">
@@ -62356,7 +62359,7 @@
         <v>295</v>
       </c>
       <c r="B296">
-        <v>7476864</v>
+        <v>7476857</v>
       </c>
       <c r="C296" t="s">
         <v>68</v>
@@ -62371,43 +62374,43 @@
         <v>27</v>
       </c>
       <c r="G296" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H296" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I296">
         <v>0</v>
       </c>
       <c r="J296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L296">
         <v>0</v>
       </c>
       <c r="M296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O296" t="s">
         <v>101</v>
       </c>
       <c r="P296" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="Q296">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R296">
         <v>2.1</v>
       </c>
       <c r="S296">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T296">
         <v>1.4</v>
@@ -62422,121 +62425,121 @@
         <v>1.36</v>
       </c>
       <c r="X296">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y296">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z296">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AA296">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AB296">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="AC296">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AD296">
+        <v>8.5</v>
+      </c>
+      <c r="AE296">
+        <v>1.33</v>
+      </c>
+      <c r="AF296">
+        <v>3.25</v>
+      </c>
+      <c r="AG296">
+        <v>1.9</v>
+      </c>
+      <c r="AH296">
+        <v>1.8</v>
+      </c>
+      <c r="AI296">
+        <v>1.73</v>
+      </c>
+      <c r="AJ296">
+        <v>2</v>
+      </c>
+      <c r="AK296">
+        <v>1.33</v>
+      </c>
+      <c r="AL296">
+        <v>1.28</v>
+      </c>
+      <c r="AM296">
+        <v>1.65</v>
+      </c>
+      <c r="AN296">
+        <v>1.25</v>
+      </c>
+      <c r="AO296">
+        <v>0.91</v>
+      </c>
+      <c r="AP296">
+        <v>1.15</v>
+      </c>
+      <c r="AQ296">
+        <v>1.08</v>
+      </c>
+      <c r="AR296">
+        <v>1.46</v>
+      </c>
+      <c r="AS296">
+        <v>1.04</v>
+      </c>
+      <c r="AT296">
+        <v>2.5</v>
+      </c>
+      <c r="AU296">
+        <v>2</v>
+      </c>
+      <c r="AV296">
+        <v>6</v>
+      </c>
+      <c r="AW296">
+        <v>14</v>
+      </c>
+      <c r="AX296">
+        <v>4</v>
+      </c>
+      <c r="AY296">
+        <v>20</v>
+      </c>
+      <c r="AZ296">
+        <v>12</v>
+      </c>
+      <c r="BA296">
         <v>8</v>
       </c>
-      <c r="AE296">
-        <v>1.35</v>
-      </c>
-      <c r="AF296">
-        <v>3.1</v>
-      </c>
-      <c r="AG296">
-        <v>2</v>
-      </c>
-      <c r="AH296">
-        <v>1.72</v>
-      </c>
-      <c r="AI296">
-        <v>1.8</v>
-      </c>
-      <c r="AJ296">
-        <v>1.91</v>
-      </c>
-      <c r="AK296">
-        <v>1.25</v>
-      </c>
-      <c r="AL296">
-        <v>1.25</v>
-      </c>
-      <c r="AM296">
-        <v>1.77</v>
-      </c>
-      <c r="AN296">
-        <v>2</v>
-      </c>
-      <c r="AO296">
-        <v>1.1</v>
-      </c>
-      <c r="AP296">
-        <v>1.85</v>
-      </c>
-      <c r="AQ296">
-        <v>1.27</v>
-      </c>
-      <c r="AR296">
-        <v>1.45</v>
-      </c>
-      <c r="AS296">
-        <v>1.13</v>
-      </c>
-      <c r="AT296">
-        <v>2.58</v>
-      </c>
-      <c r="AU296">
-        <v>5</v>
-      </c>
-      <c r="AV296">
+      <c r="BB296">
         <v>4</v>
       </c>
-      <c r="AW296">
-        <v>8</v>
-      </c>
-      <c r="AX296">
-        <v>8</v>
-      </c>
-      <c r="AY296">
-        <v>14</v>
-      </c>
-      <c r="AZ296">
-        <v>14</v>
-      </c>
-      <c r="BA296">
-        <v>2</v>
-      </c>
-      <c r="BB296">
-        <v>3</v>
-      </c>
       <c r="BC296">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BD296">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="BE296">
         <v>6.75</v>
       </c>
       <c r="BF296">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="BG296">
         <v>1.3</v>
       </c>
       <c r="BH296">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BI296">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BJ296">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="BK296">
         <v>1.85</v>
@@ -62562,7 +62565,7 @@
         <v>296</v>
       </c>
       <c r="B297">
-        <v>7476866</v>
+        <v>7476856</v>
       </c>
       <c r="C297" t="s">
         <v>68</v>
@@ -62577,43 +62580,43 @@
         <v>27</v>
       </c>
       <c r="G297" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H297" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="I297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K297">
         <v>2</v>
       </c>
       <c r="L297">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M297">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N297">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O297" t="s">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="P297" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q297">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="R297">
         <v>2.25</v>
       </c>
       <c r="S297">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="T297">
         <v>1.36</v>
@@ -62634,133 +62637,133 @@
         <v>1.1</v>
       </c>
       <c r="Z297">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="AA297">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AB297">
-        <v>3.34</v>
+        <v>2.19</v>
       </c>
       <c r="AC297">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD297">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="AE297">
         <v>1.25</v>
       </c>
       <c r="AF297">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AG297">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH297">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AI297">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AJ297">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AK297">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="AL297">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM297">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AN297">
-        <v>2.46</v>
+        <v>1.27</v>
       </c>
       <c r="AO297">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AP297">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ297">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="AR297">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AS297">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AT297">
-        <v>3.06</v>
+        <v>2.58</v>
       </c>
       <c r="AU297">
+        <v>3</v>
+      </c>
+      <c r="AV297">
+        <v>6</v>
+      </c>
+      <c r="AW297">
+        <v>3</v>
+      </c>
+      <c r="AX297">
+        <v>4</v>
+      </c>
+      <c r="AY297">
+        <v>6</v>
+      </c>
+      <c r="AZ297">
         <v>10</v>
       </c>
-      <c r="AV297">
-        <v>4</v>
-      </c>
-      <c r="AW297">
-        <v>16</v>
-      </c>
-      <c r="AX297">
-        <v>3</v>
-      </c>
-      <c r="AY297">
-        <v>26</v>
-      </c>
-      <c r="AZ297">
-        <v>7</v>
-      </c>
       <c r="BA297">
+        <v>2</v>
+      </c>
+      <c r="BB297">
+        <v>6</v>
+      </c>
+      <c r="BC297">
         <v>8</v>
       </c>
-      <c r="BB297">
-        <v>2</v>
-      </c>
-      <c r="BC297">
-        <v>10</v>
-      </c>
       <c r="BD297">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="BE297">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF297">
-        <v>2.48</v>
+        <v>1.8</v>
       </c>
       <c r="BG297">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="BH297">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="BI297">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="BJ297">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="BK297">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="BL297">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="BM297">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="BN297">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="BO297">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="BP297">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="298" spans="1:68">
@@ -62768,7 +62771,7 @@
         <v>297</v>
       </c>
       <c r="B298">
-        <v>7476865</v>
+        <v>7476855</v>
       </c>
       <c r="C298" t="s">
         <v>68</v>
@@ -62783,19 +62786,19 @@
         <v>27</v>
       </c>
       <c r="G298" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H298" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J298">
         <v>0</v>
       </c>
       <c r="K298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L298">
         <v>2</v>
@@ -62807,19 +62810,19 @@
         <v>2</v>
       </c>
       <c r="O298" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P298" t="s">
         <v>101</v>
       </c>
       <c r="Q298">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="R298">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S298">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="T298">
         <v>1.44</v>
@@ -62840,13 +62843,13 @@
         <v>1.07</v>
       </c>
       <c r="Z298">
-        <v>2.46</v>
+        <v>1.62</v>
       </c>
       <c r="AA298">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="AB298">
-        <v>2.51</v>
+        <v>4.49</v>
       </c>
       <c r="AC298">
         <v>1.07</v>
@@ -62855,118 +62858,118 @@
         <v>8</v>
       </c>
       <c r="AE298">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF298">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AG298">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH298">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AI298">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AJ298">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK298">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="AL298">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AM298">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AN298">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AO298">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP298">
-        <v>1.38</v>
+        <v>2.08</v>
       </c>
       <c r="AQ298">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="AR298">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AS298">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AT298">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="AU298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV298">
         <v>3</v>
       </c>
       <c r="AW298">
+        <v>3</v>
+      </c>
+      <c r="AX298">
         <v>10</v>
       </c>
-      <c r="AX298">
-        <v>5</v>
-      </c>
       <c r="AY298">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ298">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA298">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BB298">
         <v>4</v>
       </c>
       <c r="BC298">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BD298">
-        <v>2.05</v>
+        <v>1.52</v>
       </c>
       <c r="BE298">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF298">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="BG298">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="BH298">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="BI298">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="BJ298">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="BK298">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="BL298">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="BM298">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BN298">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO298">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BP298">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="299" spans="1:68">
@@ -62974,7 +62977,7 @@
         <v>298</v>
       </c>
       <c r="B299">
-        <v>7476855</v>
+        <v>7476866</v>
       </c>
       <c r="C299" t="s">
         <v>68</v>
@@ -62989,187 +62992,187 @@
         <v>27</v>
       </c>
       <c r="G299" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H299" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K299">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L299">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M299">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N299">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O299" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P299" t="s">
-        <v>101</v>
+        <v>398</v>
       </c>
       <c r="Q299">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R299">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S299">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="T299">
+        <v>1.36</v>
+      </c>
+      <c r="U299">
+        <v>3</v>
+      </c>
+      <c r="V299">
+        <v>2.63</v>
+      </c>
+      <c r="W299">
         <v>1.44</v>
       </c>
-      <c r="U299">
-        <v>2.63</v>
-      </c>
-      <c r="V299">
-        <v>3.25</v>
-      </c>
-      <c r="W299">
-        <v>1.33</v>
-      </c>
       <c r="X299">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y299">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z299">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AA299">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="AB299">
-        <v>4.49</v>
+        <v>3.34</v>
       </c>
       <c r="AC299">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AD299">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AE299">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AF299">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AG299">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AH299">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AI299">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ299">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AK299">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL299">
         <v>1.22</v>
       </c>
       <c r="AM299">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AN299">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="AO299">
-        <v>0.67</v>
+        <v>1.44</v>
       </c>
       <c r="AP299">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AQ299">
-        <v>0.62</v>
+        <v>1.18</v>
       </c>
       <c r="AR299">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AS299">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AT299">
-        <v>2.58</v>
+        <v>3.06</v>
       </c>
       <c r="AU299">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AV299">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW299">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AX299">
+        <v>3</v>
+      </c>
+      <c r="AY299">
+        <v>26</v>
+      </c>
+      <c r="AZ299">
+        <v>7</v>
+      </c>
+      <c r="BA299">
+        <v>8</v>
+      </c>
+      <c r="BB299">
+        <v>2</v>
+      </c>
+      <c r="BC299">
         <v>10</v>
       </c>
-      <c r="AY299">
-        <v>11</v>
-      </c>
-      <c r="AZ299">
-        <v>15</v>
-      </c>
-      <c r="BA299">
-        <v>1</v>
-      </c>
-      <c r="BB299">
-        <v>4</v>
-      </c>
-      <c r="BC299">
-        <v>5</v>
-      </c>
       <c r="BD299">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="BE299">
         <v>6.4</v>
       </c>
       <c r="BF299">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="BG299">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BH299">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="BI299">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BJ299">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BK299">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="BL299">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BM299">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="BN299">
         <v>1.43</v>
       </c>
       <c r="BO299">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP299">
         <v>1.25</v>
@@ -63180,7 +63183,7 @@
         <v>299</v>
       </c>
       <c r="B300">
-        <v>7476856</v>
+        <v>7476864</v>
       </c>
       <c r="C300" t="s">
         <v>68</v>
@@ -63195,10 +63198,10 @@
         <v>27</v>
       </c>
       <c r="G300" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H300" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I300">
         <v>0</v>
@@ -63213,172 +63216,172 @@
         <v>0</v>
       </c>
       <c r="M300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O300" t="s">
         <v>101</v>
       </c>
       <c r="P300" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q300">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="R300">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S300">
+        <v>4</v>
+      </c>
+      <c r="T300">
+        <v>1.4</v>
+      </c>
+      <c r="U300">
         <v>2.75</v>
       </c>
-      <c r="T300">
+      <c r="V300">
+        <v>3</v>
+      </c>
+      <c r="W300">
         <v>1.36</v>
       </c>
-      <c r="U300">
-        <v>3</v>
-      </c>
-      <c r="V300">
-        <v>2.63</v>
-      </c>
-      <c r="W300">
-        <v>1.44</v>
-      </c>
       <c r="X300">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y300">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z300">
-        <v>2.74</v>
+        <v>2.02</v>
       </c>
       <c r="AA300">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="AB300">
-        <v>2.19</v>
+        <v>3.23</v>
       </c>
       <c r="AC300">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AD300">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE300">
+        <v>1.35</v>
+      </c>
+      <c r="AF300">
+        <v>3.1</v>
+      </c>
+      <c r="AG300">
+        <v>2</v>
+      </c>
+      <c r="AH300">
+        <v>1.72</v>
+      </c>
+      <c r="AI300">
+        <v>1.8</v>
+      </c>
+      <c r="AJ300">
+        <v>1.91</v>
+      </c>
+      <c r="AK300">
         <v>1.25</v>
-      </c>
-      <c r="AF300">
-        <v>3.75</v>
-      </c>
-      <c r="AG300">
-        <v>1.8</v>
-      </c>
-      <c r="AH300">
-        <v>2</v>
-      </c>
-      <c r="AI300">
-        <v>1.62</v>
-      </c>
-      <c r="AJ300">
-        <v>2.2</v>
-      </c>
-      <c r="AK300">
-        <v>1.72</v>
       </c>
       <c r="AL300">
         <v>1.25</v>
       </c>
       <c r="AM300">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="AN300">
+        <v>2</v>
+      </c>
+      <c r="AO300">
+        <v>1.1</v>
+      </c>
+      <c r="AP300">
+        <v>1.85</v>
+      </c>
+      <c r="AQ300">
         <v>1.27</v>
       </c>
-      <c r="AO300">
-        <v>1.54</v>
-      </c>
-      <c r="AP300">
-        <v>1.17</v>
-      </c>
-      <c r="AQ300">
-        <v>1.64</v>
-      </c>
       <c r="AR300">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AS300">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AT300">
         <v>2.58</v>
       </c>
       <c r="AU300">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV300">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW300">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX300">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY300">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AZ300">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA300">
         <v>2</v>
       </c>
       <c r="BB300">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BC300">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BD300">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="BE300">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF300">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="BG300">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BH300">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI300">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="BJ300">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="BK300">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BL300">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="BM300">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="BN300">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="BO300">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BP300">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="301" spans="1:68">
@@ -63386,7 +63389,7 @@
         <v>300</v>
       </c>
       <c r="B301">
-        <v>7476862</v>
+        <v>7476863</v>
       </c>
       <c r="C301" t="s">
         <v>68</v>
@@ -63401,88 +63404,88 @@
         <v>27</v>
       </c>
       <c r="G301" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H301" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J301">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K301">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L301">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N301">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O301" t="s">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="P301" t="s">
-        <v>291</v>
+        <v>400</v>
       </c>
       <c r="Q301">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R301">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S301">
-        <v>2.88</v>
+        <v>6.5</v>
       </c>
       <c r="T301">
+        <v>1.36</v>
+      </c>
+      <c r="U301">
+        <v>3</v>
+      </c>
+      <c r="V301">
+        <v>2.63</v>
+      </c>
+      <c r="W301">
         <v>1.44</v>
       </c>
-      <c r="U301">
-        <v>2.63</v>
-      </c>
-      <c r="V301">
-        <v>3.25</v>
-      </c>
-      <c r="W301">
-        <v>1.33</v>
-      </c>
       <c r="X301">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y301">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z301">
-        <v>3.13</v>
+        <v>1.39</v>
       </c>
       <c r="AA301">
-        <v>3.03</v>
+        <v>3.91</v>
       </c>
       <c r="AB301">
-        <v>2.03</v>
+        <v>5.9</v>
       </c>
       <c r="AC301">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AD301">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE301">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AF301">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AG301">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AH301">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AI301">
         <v>1.83</v>
@@ -63491,100 +63494,100 @@
         <v>1.83</v>
       </c>
       <c r="AK301">
+        <v>1.11</v>
+      </c>
+      <c r="AL301">
+        <v>1.17</v>
+      </c>
+      <c r="AM301">
+        <v>2.7</v>
+      </c>
+      <c r="AN301">
+        <v>1.55</v>
+      </c>
+      <c r="AO301">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP301">
         <v>1.67</v>
       </c>
-      <c r="AL301">
-        <v>1.28</v>
-      </c>
-      <c r="AM301">
-        <v>1.3</v>
-      </c>
-      <c r="AN301">
-        <v>0.55</v>
-      </c>
-      <c r="AO301">
-        <v>1.38</v>
-      </c>
-      <c r="AP301">
-        <v>0.5</v>
-      </c>
       <c r="AQ301">
-        <v>1.5</v>
+        <v>0.64</v>
       </c>
       <c r="AR301">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AS301">
-        <v>1.12</v>
+        <v>0.83</v>
       </c>
       <c r="AT301">
-        <v>2.43</v>
+        <v>2.02</v>
       </c>
       <c r="AU301">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AV301">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW301">
         <v>12</v>
       </c>
       <c r="AX301">
+        <v>8</v>
+      </c>
+      <c r="AY301">
+        <v>28</v>
+      </c>
+      <c r="AZ301">
+        <v>16</v>
+      </c>
+      <c r="BA301">
+        <v>9</v>
+      </c>
+      <c r="BB301">
         <v>6</v>
       </c>
-      <c r="AY301">
-        <v>19</v>
-      </c>
-      <c r="AZ301">
-        <v>10</v>
-      </c>
-      <c r="BA301">
-        <v>7</v>
-      </c>
-      <c r="BB301">
-        <v>4</v>
-      </c>
       <c r="BC301">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BD301">
-        <v>2.43</v>
+        <v>1.38</v>
       </c>
       <c r="BE301">
         <v>6.75</v>
       </c>
       <c r="BF301">
-        <v>1.66</v>
+        <v>3.45</v>
       </c>
       <c r="BG301">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="BH301">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="BI301">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="BJ301">
-        <v>3.2</v>
+        <v>2.07</v>
       </c>
       <c r="BK301">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="BL301">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="BM301">
-        <v>1.74</v>
+        <v>2.65</v>
       </c>
       <c r="BN301">
-        <v>1.96</v>
+        <v>1.42</v>
       </c>
       <c r="BO301">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="BP301">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="302" spans="1:68">
@@ -63592,7 +63595,7 @@
         <v>301</v>
       </c>
       <c r="B302">
-        <v>7476849</v>
+        <v>7476741</v>
       </c>
       <c r="C302" t="s">
         <v>68</v>
@@ -63604,193 +63607,193 @@
         <v>45678.69791666666</v>
       </c>
       <c r="F302">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G302" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H302" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J302">
         <v>0</v>
       </c>
       <c r="K302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L302">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O302" t="s">
-        <v>101</v>
+        <v>277</v>
       </c>
       <c r="P302" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="Q302">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="R302">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S302">
+        <v>3.4</v>
+      </c>
+      <c r="T302">
+        <v>1.33</v>
+      </c>
+      <c r="U302">
+        <v>3.25</v>
+      </c>
+      <c r="V302">
         <v>2.63</v>
       </c>
-      <c r="T302">
+      <c r="W302">
         <v>1.44</v>
       </c>
-      <c r="U302">
-        <v>2.63</v>
-      </c>
-      <c r="V302">
-        <v>3.25</v>
-      </c>
-      <c r="W302">
+      <c r="X302">
+        <v>7</v>
+      </c>
+      <c r="Y302">
+        <v>1.1</v>
+      </c>
+      <c r="Z302">
+        <v>2.3</v>
+      </c>
+      <c r="AA302">
+        <v>3.6</v>
+      </c>
+      <c r="AB302">
+        <v>2.9</v>
+      </c>
+      <c r="AC302">
+        <v>1.05</v>
+      </c>
+      <c r="AD302">
+        <v>9</v>
+      </c>
+      <c r="AE302">
+        <v>1.28</v>
+      </c>
+      <c r="AF302">
+        <v>3.55</v>
+      </c>
+      <c r="AG302">
+        <v>1.75</v>
+      </c>
+      <c r="AH302">
+        <v>1.95</v>
+      </c>
+      <c r="AI302">
+        <v>1.62</v>
+      </c>
+      <c r="AJ302">
+        <v>2.2</v>
+      </c>
+      <c r="AK302">
+        <v>1.45</v>
+      </c>
+      <c r="AL302">
+        <v>1.25</v>
+      </c>
+      <c r="AM302">
+        <v>1.48</v>
+      </c>
+      <c r="AN302">
         <v>1.33</v>
       </c>
-      <c r="X302">
-        <v>10</v>
-      </c>
-      <c r="Y302">
-        <v>1.06</v>
-      </c>
-      <c r="Z302">
-        <v>3.7</v>
-      </c>
-      <c r="AA302">
-        <v>3.4</v>
-      </c>
-      <c r="AB302">
-        <v>2.05</v>
-      </c>
-      <c r="AC302">
-        <v>1.06</v>
-      </c>
-      <c r="AD302">
-        <v>9.5</v>
-      </c>
-      <c r="AE302">
-        <v>1.38</v>
-      </c>
-      <c r="AF302">
-        <v>3</v>
-      </c>
-      <c r="AG302">
-        <v>2.1</v>
-      </c>
-      <c r="AH302">
-        <v>1.67</v>
-      </c>
-      <c r="AI302">
-        <v>1.91</v>
-      </c>
-      <c r="AJ302">
-        <v>1.8</v>
-      </c>
-      <c r="AK302">
-        <v>1.75</v>
-      </c>
-      <c r="AL302">
+      <c r="AO302">
+        <v>1.3</v>
+      </c>
+      <c r="AP302">
+        <v>1.46</v>
+      </c>
+      <c r="AQ302">
+        <v>1.18</v>
+      </c>
+      <c r="AR302">
         <v>1.31</v>
       </c>
-      <c r="AM302">
-        <v>1.27</v>
-      </c>
-      <c r="AN302">
-        <v>1.15</v>
-      </c>
-      <c r="AO302">
-        <v>1.08</v>
-      </c>
-      <c r="AP302">
-        <v>1.14</v>
-      </c>
-      <c r="AQ302">
-        <v>1.08</v>
-      </c>
-      <c r="AR302">
-        <v>1.08</v>
-      </c>
       <c r="AS302">
-        <v>1.07</v>
+        <v>1.42</v>
       </c>
       <c r="AT302">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="AU302">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV302">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW302">
         <v>7</v>
       </c>
       <c r="AX302">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AY302">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ302">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="BA302">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB302">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BC302">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BD302">
-        <v>2.85</v>
+        <v>1.82</v>
       </c>
       <c r="BE302">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF302">
-        <v>1.65</v>
+        <v>2.43</v>
       </c>
       <c r="BG302">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BH302">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="BI302">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="BJ302">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="BK302">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="BL302">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="BM302">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="BN302">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="BO302">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BP302">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="303" spans="1:68">
@@ -63798,7 +63801,7 @@
         <v>302</v>
       </c>
       <c r="B303">
-        <v>7476741</v>
+        <v>7476849</v>
       </c>
       <c r="C303" t="s">
         <v>68</v>
@@ -63810,192 +63813,398 @@
         <v>45678.69791666666</v>
       </c>
       <c r="F303">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G303" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H303" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I303">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J303">
         <v>0</v>
       </c>
       <c r="K303">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L303">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M303">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N303">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O303" t="s">
-        <v>277</v>
+        <v>101</v>
       </c>
       <c r="P303" t="s">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="Q303">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="R303">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S303">
+        <v>2.63</v>
+      </c>
+      <c r="T303">
+        <v>1.44</v>
+      </c>
+      <c r="U303">
+        <v>2.63</v>
+      </c>
+      <c r="V303">
+        <v>3.25</v>
+      </c>
+      <c r="W303">
+        <v>1.33</v>
+      </c>
+      <c r="X303">
+        <v>10</v>
+      </c>
+      <c r="Y303">
+        <v>1.06</v>
+      </c>
+      <c r="Z303">
+        <v>3.7</v>
+      </c>
+      <c r="AA303">
         <v>3.4</v>
       </c>
-      <c r="T303">
-        <v>1.33</v>
-      </c>
-      <c r="U303">
-        <v>3.25</v>
-      </c>
-      <c r="V303">
-        <v>2.63</v>
-      </c>
-      <c r="W303">
-        <v>1.44</v>
-      </c>
-      <c r="X303">
-        <v>7</v>
-      </c>
-      <c r="Y303">
-        <v>1.1</v>
-      </c>
-      <c r="Z303">
-        <v>2.3</v>
-      </c>
-      <c r="AA303">
-        <v>3.6</v>
-      </c>
       <c r="AB303">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC303">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD303">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AE303">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AF303">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="AG303">
+        <v>2.1</v>
+      </c>
+      <c r="AH303">
+        <v>1.67</v>
+      </c>
+      <c r="AI303">
+        <v>1.91</v>
+      </c>
+      <c r="AJ303">
+        <v>1.8</v>
+      </c>
+      <c r="AK303">
         <v>1.75</v>
       </c>
-      <c r="AH303">
-        <v>1.95</v>
-      </c>
-      <c r="AI303">
-        <v>1.62</v>
-      </c>
-      <c r="AJ303">
-        <v>2.2</v>
-      </c>
-      <c r="AK303">
-        <v>1.45</v>
-      </c>
       <c r="AL303">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AM303">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AN303">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AO303">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AP303">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="AQ303">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR303">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AS303">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="AT303">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AU303">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AV303">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW303">
         <v>7</v>
       </c>
       <c r="AX303">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AY303">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ303">
+        <v>22</v>
+      </c>
+      <c r="BA303">
+        <v>1</v>
+      </c>
+      <c r="BB303">
+        <v>8</v>
+      </c>
+      <c r="BC303">
+        <v>9</v>
+      </c>
+      <c r="BD303">
+        <v>2.85</v>
+      </c>
+      <c r="BE303">
+        <v>6.75</v>
+      </c>
+      <c r="BF303">
+        <v>1.65</v>
+      </c>
+      <c r="BG303">
+        <v>1.18</v>
+      </c>
+      <c r="BH303">
+        <v>3.9</v>
+      </c>
+      <c r="BI303">
+        <v>1.37</v>
+      </c>
+      <c r="BJ303">
+        <v>2.75</v>
+      </c>
+      <c r="BK303">
+        <v>1.7</v>
+      </c>
+      <c r="BL303">
+        <v>2.05</v>
+      </c>
+      <c r="BM303">
+        <v>2.09</v>
+      </c>
+      <c r="BN303">
+        <v>1.63</v>
+      </c>
+      <c r="BO303">
+        <v>2.7</v>
+      </c>
+      <c r="BP303">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="304" spans="1:68">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>7476876</v>
+      </c>
+      <c r="C304" t="s">
+        <v>68</v>
+      </c>
+      <c r="D304" t="s">
+        <v>69</v>
+      </c>
+      <c r="E304" s="2">
+        <v>45681.69791666666</v>
+      </c>
+      <c r="F304">
+        <v>28</v>
+      </c>
+      <c r="G304" t="s">
+        <v>89</v>
+      </c>
+      <c r="H304" t="s">
+        <v>91</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+      <c r="J304">
+        <v>1</v>
+      </c>
+      <c r="K304">
+        <v>2</v>
+      </c>
+      <c r="L304">
+        <v>1</v>
+      </c>
+      <c r="M304">
+        <v>2</v>
+      </c>
+      <c r="N304">
+        <v>3</v>
+      </c>
+      <c r="O304" t="s">
+        <v>278</v>
+      </c>
+      <c r="P304" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q304">
+        <v>4</v>
+      </c>
+      <c r="R304">
+        <v>2.2</v>
+      </c>
+      <c r="S304">
+        <v>2.75</v>
+      </c>
+      <c r="T304">
+        <v>1.36</v>
+      </c>
+      <c r="U304">
+        <v>3</v>
+      </c>
+      <c r="V304">
+        <v>2.75</v>
+      </c>
+      <c r="W304">
+        <v>1.4</v>
+      </c>
+      <c r="X304">
         <v>7</v>
       </c>
-      <c r="BA303">
-        <v>3</v>
-      </c>
-      <c r="BB303">
-        <v>1</v>
-      </c>
-      <c r="BC303">
+      <c r="Y304">
+        <v>1.1</v>
+      </c>
+      <c r="Z304">
+        <v>3.11</v>
+      </c>
+      <c r="AA304">
+        <v>3.38</v>
+      </c>
+      <c r="AB304">
+        <v>2.21</v>
+      </c>
+      <c r="AC304">
+        <v>1.04</v>
+      </c>
+      <c r="AD304">
+        <v>13</v>
+      </c>
+      <c r="AE304">
+        <v>1.25</v>
+      </c>
+      <c r="AF304">
+        <v>3.75</v>
+      </c>
+      <c r="AG304">
+        <v>1.8</v>
+      </c>
+      <c r="AH304">
+        <v>1.94</v>
+      </c>
+      <c r="AI304">
+        <v>1.67</v>
+      </c>
+      <c r="AJ304">
+        <v>2.1</v>
+      </c>
+      <c r="AK304">
+        <v>1.78</v>
+      </c>
+      <c r="AL304">
+        <v>1.25</v>
+      </c>
+      <c r="AM304">
+        <v>1.3</v>
+      </c>
+      <c r="AN304">
+        <v>1.7</v>
+      </c>
+      <c r="AO304">
+        <v>0.71</v>
+      </c>
+      <c r="AP304">
+        <v>1.55</v>
+      </c>
+      <c r="AQ304">
+        <v>0.87</v>
+      </c>
+      <c r="AR304">
+        <v>1.29</v>
+      </c>
+      <c r="AS304">
+        <v>1.06</v>
+      </c>
+      <c r="AT304">
+        <v>2.35</v>
+      </c>
+      <c r="AU304">
         <v>4</v>
       </c>
-      <c r="BD303">
-        <v>1.82</v>
-      </c>
-      <c r="BE303">
+      <c r="AV304">
+        <v>5</v>
+      </c>
+      <c r="AW304">
+        <v>4</v>
+      </c>
+      <c r="AX304">
+        <v>6</v>
+      </c>
+      <c r="AY304">
+        <v>8</v>
+      </c>
+      <c r="AZ304">
+        <v>12</v>
+      </c>
+      <c r="BA304">
+        <v>3</v>
+      </c>
+      <c r="BB304">
         <v>7</v>
       </c>
-      <c r="BF303">
-        <v>2.43</v>
-      </c>
-      <c r="BG303">
-        <v>1.27</v>
-      </c>
-      <c r="BH303">
-        <v>3.38</v>
-      </c>
-      <c r="BI303">
-        <v>1.49</v>
-      </c>
-      <c r="BJ303">
-        <v>2.44</v>
-      </c>
-      <c r="BK303">
-        <v>1.82</v>
-      </c>
-      <c r="BL303">
-        <v>1.98</v>
-      </c>
-      <c r="BM303">
-        <v>2.32</v>
-      </c>
-      <c r="BN303">
-        <v>1.54</v>
-      </c>
-      <c r="BO303">
-        <v>3.05</v>
-      </c>
-      <c r="BP303">
+      <c r="BC304">
+        <v>10</v>
+      </c>
+      <c r="BD304">
+        <v>2.77</v>
+      </c>
+      <c r="BE304">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF304">
+        <v>1.59</v>
+      </c>
+      <c r="BG304">
+        <v>1.2</v>
+      </c>
+      <c r="BH304">
+        <v>3.72</v>
+      </c>
+      <c r="BI304">
+        <v>1.41</v>
+      </c>
+      <c r="BJ304">
+        <v>2.6</v>
+      </c>
+      <c r="BK304">
+        <v>1.77</v>
+      </c>
+      <c r="BL304">
+        <v>1.95</v>
+      </c>
+      <c r="BM304">
+        <v>2.17</v>
+      </c>
+      <c r="BN304">
+        <v>1.58</v>
+      </c>
+      <c r="BO304">
+        <v>2.83</v>
+      </c>
+      <c r="BP304">
         <v>1.33</v>
       </c>
     </row>
